--- a/tabular/reference/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/reference/herv_sublineage_ltr_data_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76280056-E2DA-2442-9F7A-6949202224D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD43313-04B4-574F-B4E9-A88774C79950}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3320" yWindow="580" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1600" yWindow="500" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ltr_lineage_table" sheetId="1" r:id="rId1"/>
@@ -1778,10 +1778,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="6" width="19.6640625" customWidth="1"/>
@@ -1844,7 +1844,7 @@
         <v>7</v>
       </c>
       <c r="I2" t="str">
-        <f t="shared" ref="I2:I33" si="0">IF(A2&lt;&gt;B2,"FLAG","")</f>
+        <f>IF(A2&lt;&gt;B2,"FLAG","")</f>
         <v>FLAG</v>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>7</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A3&lt;&gt;B3,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
         <v>17</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A4&lt;&gt;B4,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
         <v>17</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A5&lt;&gt;B5,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
         <v>17</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A6&lt;&gt;B6,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
         <v>17</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A7&lt;&gt;B7,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
         <v>17</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A8&lt;&gt;B8,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>17</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A9&lt;&gt;B9,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
         <v>17</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A10&lt;&gt;B10,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         <v>17</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A11&lt;&gt;B11,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
         <v>7</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A12&lt;&gt;B12,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
         <v>7</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A13&lt;&gt;B13,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
         <v>17</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A14&lt;&gt;B14,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>17</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A15&lt;&gt;B15,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
         <v>17</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A16&lt;&gt;B16,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
         <v>17</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A17&lt;&gt;B17,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>17</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A18&lt;&gt;B18,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>17</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A19&lt;&gt;B19,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>17</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A20&lt;&gt;B20,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>17</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A21&lt;&gt;B21,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
         <v>17</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A22&lt;&gt;B22,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
         <v>17</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         <v>17</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A24&lt;&gt;B24,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
         <v>17</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A25&lt;&gt;B25,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
         <v>17</v>
       </c>
       <c r="I26" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A26&lt;&gt;B26,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
         <v>17</v>
       </c>
       <c r="I27" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A27&lt;&gt;B27,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         <v>17</v>
       </c>
       <c r="I28" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A28&lt;&gt;B28,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
         <v>17</v>
       </c>
       <c r="I29" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A29&lt;&gt;B29,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
         <v>17</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A30&lt;&gt;B30,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>17</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A31&lt;&gt;B31,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
         <v>17</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A32&lt;&gt;B32,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
         <v>17</v>
       </c>
       <c r="I33" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(A33&lt;&gt;B33,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
         <v>17</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" ref="I34:I65" si="1">IF(A34&lt;&gt;B34,"FLAG","")</f>
+        <f>IF(A34&lt;&gt;B34,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
         <v>17</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A35&lt;&gt;B35,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
         <v>17</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A36&lt;&gt;B36,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>17</v>
       </c>
       <c r="I37" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A37&lt;&gt;B37,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>17</v>
       </c>
       <c r="I38" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A38&lt;&gt;B38,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
         <v>17</v>
       </c>
       <c r="I39" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A39&lt;&gt;B39,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
         <v>17</v>
       </c>
       <c r="I40" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A40&lt;&gt;B40,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
         <v>17</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A41&lt;&gt;B41,"FLAG","")</f>
         <v>FLAG</v>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
         <v>17</v>
       </c>
       <c r="I42" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A42&lt;&gt;B42,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>17</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A43&lt;&gt;B43,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
         <v>17</v>
       </c>
       <c r="I44" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A44&lt;&gt;B44,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
         <v>17</v>
       </c>
       <c r="I45" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A45&lt;&gt;B45,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
         <v>17</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A46&lt;&gt;B46,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
         <v>17</v>
       </c>
       <c r="I47" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A47&lt;&gt;B47,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>17</v>
       </c>
       <c r="I48" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A48&lt;&gt;B48,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
         <v>17</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A49&lt;&gt;B49,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
         <v>17</v>
       </c>
       <c r="I50" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A50&lt;&gt;B50,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
         <v>17</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A51&lt;&gt;B51,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
         <v>17</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A52&lt;&gt;B52,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
         <v>17</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A53&lt;&gt;B53,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
         <v>17</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A54&lt;&gt;B54,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         <v>17</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A55&lt;&gt;B55,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>17</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A56&lt;&gt;B56,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
         <v>17</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A57&lt;&gt;B57,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
         <v>17</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A58&lt;&gt;B58,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
         <v>17</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A59&lt;&gt;B59,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
         <v>17</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A60&lt;&gt;B60,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
         <v>17</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A61&lt;&gt;B61,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         <v>17</v>
       </c>
       <c r="I62" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A62&lt;&gt;B62,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
         <v>17</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A63&lt;&gt;B63,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
         <v>17</v>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A64&lt;&gt;B64,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
         <v>17</v>
       </c>
       <c r="I65" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(A65&lt;&gt;B65,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
         <v>17</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" ref="I66:I97" si="2">IF(A66&lt;&gt;B66,"FLAG","")</f>
+        <f>IF(A66&lt;&gt;B66,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
         <v>17</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A67&lt;&gt;B67,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
         <v>17</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A68&lt;&gt;B68,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
         <v>17</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A69&lt;&gt;B69,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
         <v>17</v>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A70&lt;&gt;B70,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>17</v>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A71&lt;&gt;B71,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
         <v>81</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A72&lt;&gt;B72,"FLAG","")</f>
         <v>FLAG</v>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
         <v>81</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A73&lt;&gt;B73,"FLAG","")</f>
         <v>FLAG</v>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
         <v>81</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A74&lt;&gt;B74,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
         <v>81</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A75&lt;&gt;B75,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>81</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A76&lt;&gt;B76,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         <v>81</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A77&lt;&gt;B77,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
         <v>17</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A78&lt;&gt;B78,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
         <v>17</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A79&lt;&gt;B79,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
         <v>17</v>
       </c>
       <c r="I80" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A80&lt;&gt;B80,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
         <v>17</v>
       </c>
       <c r="I81" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A81&lt;&gt;B81,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
         <v>17</v>
       </c>
       <c r="I82" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A82&lt;&gt;B82,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
         <v>17</v>
       </c>
       <c r="I83" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A83&lt;&gt;B83,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
         <v>17</v>
       </c>
       <c r="I84" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A84&lt;&gt;B84,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
         <v>17</v>
       </c>
       <c r="I85" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A85&lt;&gt;B85,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
         <v>17</v>
       </c>
       <c r="I86" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A86&lt;&gt;B86,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
         <v>17</v>
       </c>
       <c r="I87" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A87&lt;&gt;B87,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
         <v>17</v>
       </c>
       <c r="I88" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A88&lt;&gt;B88,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
         <v>17</v>
       </c>
       <c r="I89" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A89&lt;&gt;B89,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
         <v>17</v>
       </c>
       <c r="I90" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A90&lt;&gt;B90,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
         <v>17</v>
       </c>
       <c r="I91" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A91&lt;&gt;B91,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
         <v>17</v>
       </c>
       <c r="I92" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A92&lt;&gt;B92,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
         <v>17</v>
       </c>
       <c r="I93" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A93&lt;&gt;B93,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
         <v>17</v>
       </c>
       <c r="I94" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A94&lt;&gt;B94,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
         <v>17</v>
       </c>
       <c r="I95" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A95&lt;&gt;B95,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
         <v>17</v>
       </c>
       <c r="I96" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A96&lt;&gt;B96,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
         <v>17</v>
       </c>
       <c r="I97" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(A97&lt;&gt;B97,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
         <v>17</v>
       </c>
       <c r="I98" t="str">
-        <f t="shared" ref="I98:I109" si="3">IF(A98&lt;&gt;B98,"FLAG","")</f>
+        <f>IF(A98&lt;&gt;B98,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
         <v>17</v>
       </c>
       <c r="I99" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A99&lt;&gt;B99,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
         <v>17</v>
       </c>
       <c r="I100" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A100&lt;&gt;B100,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
         <v>6</v>
       </c>
       <c r="I101" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A101&lt;&gt;B101,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
         <v>154</v>
       </c>
       <c r="I102" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A102&lt;&gt;B102,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
         <v>154</v>
       </c>
       <c r="I103" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A103&lt;&gt;B103,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
         <v>154</v>
       </c>
       <c r="I104" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A104&lt;&gt;B104,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
         <v>154</v>
       </c>
       <c r="I105" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A105&lt;&gt;B105,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
         <v>154</v>
       </c>
       <c r="I106" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A106&lt;&gt;B106,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
         <v>154</v>
       </c>
       <c r="I107" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A107&lt;&gt;B107,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
         <v>154</v>
       </c>
       <c r="I108" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A108&lt;&gt;B108,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
         <v>154</v>
       </c>
       <c r="I109" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A109&lt;&gt;B109,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
         <v>154</v>
       </c>
       <c r="I111" t="str">
-        <f t="shared" ref="I111:I154" si="4">IF(A111&lt;&gt;B111,"FLAG","")</f>
+        <f>IF(A111&lt;&gt;B111,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>154</v>
       </c>
       <c r="I112" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A112&lt;&gt;B112,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
         <v>154</v>
       </c>
       <c r="I113" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A113&lt;&gt;B113,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
         <v>154</v>
       </c>
       <c r="I114" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A114&lt;&gt;B114,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
         <v>154</v>
       </c>
       <c r="I115" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A115&lt;&gt;B115,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
         <v>154</v>
       </c>
       <c r="I116" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A116&lt;&gt;B116,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
         <v>154</v>
       </c>
       <c r="I117" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A117&lt;&gt;B117,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
         <v>154</v>
       </c>
       <c r="I118" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A118&lt;&gt;B118,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
         <v>154</v>
       </c>
       <c r="I119" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A119&lt;&gt;B119,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
         <v>154</v>
       </c>
       <c r="I120" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A120&lt;&gt;B120,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
         <v>154</v>
       </c>
       <c r="I121" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A121&lt;&gt;B121,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
         <v>17</v>
       </c>
       <c r="I122" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A122&lt;&gt;B122,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
         <v>17</v>
       </c>
       <c r="I123" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A123&lt;&gt;B123,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
         <v>17</v>
       </c>
       <c r="I124" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A124&lt;&gt;B124,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
         <v>17</v>
       </c>
       <c r="I125" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A125&lt;&gt;B125,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
         <v>17</v>
       </c>
       <c r="I126" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A126&lt;&gt;B126,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
         <v>17</v>
       </c>
       <c r="I127" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A127&lt;&gt;B127,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
         <v>17</v>
       </c>
       <c r="I128" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A128&lt;&gt;B128,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
         <v>17</v>
       </c>
       <c r="I129" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A129&lt;&gt;B129,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
         <v>17</v>
       </c>
       <c r="I130" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A130&lt;&gt;B130,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
         <v>17</v>
       </c>
       <c r="I131" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A131&lt;&gt;B131,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
         <v>17</v>
       </c>
       <c r="I132" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A132&lt;&gt;B132,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
         <v>17</v>
       </c>
       <c r="I133" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A133&lt;&gt;B133,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
         <v>17</v>
       </c>
       <c r="I134" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A134&lt;&gt;B134,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
         <v>17</v>
       </c>
       <c r="I135" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A135&lt;&gt;B135,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
         <v>17</v>
       </c>
       <c r="I136" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A136&lt;&gt;B136,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
         <v>17</v>
       </c>
       <c r="I137" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A137&lt;&gt;B137,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
         <v>17</v>
       </c>
       <c r="I138" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A138&lt;&gt;B138,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -5950,7 +5950,7 @@
         <v>17</v>
       </c>
       <c r="I139" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A139&lt;&gt;B139,"FLAG","")</f>
         <v>FLAG</v>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
         <v>17</v>
       </c>
       <c r="I140" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A140&lt;&gt;B140,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
         <v>17</v>
       </c>
       <c r="I141" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A141&lt;&gt;B141,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
         <v>17</v>
       </c>
       <c r="I142" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A142&lt;&gt;B142,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
         <v>17</v>
       </c>
       <c r="I143" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A143&lt;&gt;B143,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
         <v>17</v>
       </c>
       <c r="I144" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A144&lt;&gt;B144,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
         <v>17</v>
       </c>
       <c r="I145" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A145&lt;&gt;B145,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
         <v>17</v>
       </c>
       <c r="I146" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A146&lt;&gt;B146,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -6190,25 +6190,25 @@
         <v>17</v>
       </c>
       <c r="I147" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A147&lt;&gt;B147,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A148" s="2" t="s">
-        <v>205</v>
+      <c r="A148" t="s">
+        <v>223</v>
       </c>
       <c r="B148" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C148" t="s">
         <v>249</v>
       </c>
       <c r="D148" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="E148" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>252</v>
@@ -6220,16 +6220,16 @@
         <v>17</v>
       </c>
       <c r="I148" t="str">
-        <f t="shared" si="4"/>
-        <v>FLAG</v>
+        <f>IF(A148&lt;&gt;B148,"FLAG","")</f>
+        <v/>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B149" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C149" t="s">
         <v>249</v>
@@ -6250,25 +6250,25 @@
         <v>17</v>
       </c>
       <c r="I149" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A149&lt;&gt;B149,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B150" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C150" t="s">
         <v>249</v>
       </c>
       <c r="D150" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E150" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>252</v>
@@ -6280,16 +6280,16 @@
         <v>17</v>
       </c>
       <c r="I150" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A150&lt;&gt;B150,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B151" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C151" t="s">
         <v>249</v>
@@ -6310,16 +6310,16 @@
         <v>17</v>
       </c>
       <c r="I151" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A151&lt;&gt;B151,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B152" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C152" t="s">
         <v>249</v>
@@ -6340,25 +6340,25 @@
         <v>17</v>
       </c>
       <c r="I152" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A152&lt;&gt;B152,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B153" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C153" t="s">
         <v>249</v>
       </c>
       <c r="D153" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E153" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>252</v>
@@ -6370,64 +6370,19 @@
         <v>17</v>
       </c>
       <c r="I153" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
-        <v>229</v>
-      </c>
-      <c r="B154" t="s">
-        <v>229</v>
-      </c>
-      <c r="C154" t="s">
-        <v>249</v>
-      </c>
-      <c r="D154" t="s">
-        <v>230</v>
-      </c>
-      <c r="E154" t="s">
-        <v>230</v>
-      </c>
-      <c r="F154" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G154" t="s">
-        <v>183</v>
-      </c>
-      <c r="H154" t="s">
-        <v>17</v>
-      </c>
-      <c r="I154" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(A153&lt;&gt;B153,"FLAG","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I154">
-    <sortCondition ref="F2:F154"/>
-    <sortCondition ref="C2:C154"/>
-    <sortCondition ref="E2:E154"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I153">
+    <sortCondition ref="F2:F153"/>
+    <sortCondition ref="C2:C153"/>
+    <sortCondition ref="E2:E153"/>
   </sortState>
-  <conditionalFormatting sqref="I148">
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I148)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I151:I152">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I151)))</formula>
+  <conditionalFormatting sqref="I150:I151">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I150)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -6440,9 +6395,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I149:I150">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I149)))</formula>
+  <conditionalFormatting sqref="I148:I149">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I148)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -6456,7 +6411,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107:I147 I2:I105">
-    <cfRule type="containsText" dxfId="2" priority="11" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -6471,7 +6426,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I106">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I106)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -6491,7 +6446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC7E8D0-101B-584C-9021-A7CDF92F27AF}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -7145,10 +7100,55 @@
         <v/>
       </c>
     </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" t="s">
+        <v>249</v>
+      </c>
+      <c r="D23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" t="s">
+        <v>183</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G23" t="s">
+        <v>183</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="str">
+        <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
+        <v>FLAG</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>

--- a/tabular/reference/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/reference/herv_sublineage_ltr_data_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD43313-04B4-574F-B4E9-A88774C79950}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2853C645-5490-4545-BDFB-EEBFB6185980}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="500" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="500" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ltr_lineage_table" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="203">
   <si>
     <t>LTR_name</t>
   </si>
@@ -67,66 +67,9 @@
     <t>phylogeny_subgroup</t>
   </si>
   <si>
-    <t>HERV1_LTR</t>
-  </si>
-  <si>
-    <t>HERV1_LTRa</t>
-  </si>
-  <si>
-    <t>Gamma</t>
-  </si>
-  <si>
-    <t>Eta</t>
-  </si>
-  <si>
-    <t>HERV-1</t>
-  </si>
-  <si>
-    <t>LTR35A</t>
-  </si>
-  <si>
-    <t>LTR2B</t>
-  </si>
-  <si>
-    <t>HERV-Ea</t>
-  </si>
-  <si>
-    <t>LTR2C</t>
-  </si>
-  <si>
-    <t>LTR15</t>
-  </si>
-  <si>
-    <t>RRHERV-I</t>
-  </si>
-  <si>
-    <t>LTR71A</t>
-  </si>
-  <si>
-    <t>Iota</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>HERV-ADP</t>
-  </si>
-  <si>
-    <t>LTR71B</t>
-  </si>
-  <si>
-    <t>LTR10A</t>
-  </si>
-  <si>
-    <t>HERV-IP</t>
-  </si>
-  <si>
-    <t>LTR10D</t>
-  </si>
-  <si>
-    <t>LTR10F</t>
-  </si>
-  <si>
     <t>LTR26E</t>
   </si>
   <si>
@@ -142,12 +85,6 @@
     <t>Theta</t>
   </si>
   <si>
-    <t>LTR24B</t>
-  </si>
-  <si>
-    <t>HERV-24b</t>
-  </si>
-  <si>
     <t>HERV-38</t>
   </si>
   <si>
@@ -418,12 +355,6 @@
     <t>LTR28C</t>
   </si>
   <si>
-    <t>LTR25</t>
-  </si>
-  <si>
-    <t>HUERS-P3B</t>
-  </si>
-  <si>
     <t>MER41A</t>
   </si>
   <si>
@@ -505,99 +436,6 @@
     <t>LTR60</t>
   </si>
   <si>
-    <t>MER41C</t>
-  </si>
-  <si>
-    <t>PRIMA41</t>
-  </si>
-  <si>
-    <t>Beta</t>
-  </si>
-  <si>
-    <t>LTR14A</t>
-  </si>
-  <si>
-    <t>Kappa</t>
-  </si>
-  <si>
-    <t>HERV-K(HML1)</t>
-  </si>
-  <si>
-    <t>LTR14B</t>
-  </si>
-  <si>
-    <t>LTR14</t>
-  </si>
-  <si>
-    <t>HERV-K(HML10)</t>
-  </si>
-  <si>
-    <t>LTR22</t>
-  </si>
-  <si>
-    <t>HERV-K(HML2)</t>
-  </si>
-  <si>
-    <t>LTR5</t>
-  </si>
-  <si>
-    <t>LTR5A</t>
-  </si>
-  <si>
-    <t>LTR5B</t>
-  </si>
-  <si>
-    <t>LTR5_Hs</t>
-  </si>
-  <si>
-    <t>MER9B</t>
-  </si>
-  <si>
-    <t>HERV-K(HML3)</t>
-  </si>
-  <si>
-    <t>MER9a1</t>
-  </si>
-  <si>
-    <t>MER9a2</t>
-  </si>
-  <si>
-    <t>MER9a3</t>
-  </si>
-  <si>
-    <t>LTR13</t>
-  </si>
-  <si>
-    <t>HERV-K(HML4)</t>
-  </si>
-  <si>
-    <t>LTR13A</t>
-  </si>
-  <si>
-    <t>MER11D</t>
-  </si>
-  <si>
-    <t>HERV-K(HML7)</t>
-  </si>
-  <si>
-    <t>MER11A</t>
-  </si>
-  <si>
-    <t>HERV-K(HML8)</t>
-  </si>
-  <si>
-    <t>MER11B</t>
-  </si>
-  <si>
-    <t>MER11C</t>
-  </si>
-  <si>
-    <t>LTR14C</t>
-  </si>
-  <si>
-    <t>HERV-K(HML9)</t>
-  </si>
-  <si>
     <t>LTR85b</t>
   </si>
   <si>
@@ -685,9 +523,6 @@
     <t>LTR40A1</t>
   </si>
   <si>
-    <t>HERVL40</t>
-  </si>
-  <si>
     <t>LTR40A</t>
   </si>
   <si>
@@ -709,9 +544,6 @@
     <t>MER68</t>
   </si>
   <si>
-    <t>HERVL68</t>
-  </si>
-  <si>
     <t>MER68B</t>
   </si>
   <si>
@@ -799,9 +631,6 @@
     <t>erv_1</t>
   </si>
   <si>
-    <t>erv_2</t>
-  </si>
-  <si>
     <t>erv_3</t>
   </si>
   <si>
@@ -823,38 +652,23 @@
     <t>HERV-31</t>
   </si>
   <si>
-    <t>HERV-K-HML1</t>
-  </si>
-  <si>
-    <t>HERV-K-HML10</t>
-  </si>
-  <si>
-    <t>HERV-K-HML2</t>
-  </si>
-  <si>
-    <t>HERV-K-HML3</t>
-  </si>
-  <si>
-    <t>HERV-K-HML4</t>
-  </si>
-  <si>
-    <t>HERV-K-HML7</t>
-  </si>
-  <si>
-    <t>HERV-K-HML8</t>
-  </si>
-  <si>
-    <t>HERV-K-HML9</t>
-  </si>
-  <si>
-    <t>LTR22A</t>
+    <t>HERV-L40</t>
+  </si>
+  <si>
+    <t>HERV-L68</t>
+  </si>
+  <si>
+    <t>HERV-52</t>
+  </si>
+  <si>
+    <t>LTR-53</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -996,8 +810,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1195,6 +1015,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.24994659260841701"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1356,12 +1182,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1407,17 +1234,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1778,13 +1595,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="6" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="6" width="19.6640625" customWidth="1"/>
     <col min="7" max="7" width="12.1640625" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
@@ -1797,16 +1615,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -1815,63 +1633,63 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>252</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2" t="str">
         <f>IF(A2&lt;&gt;B2,"FLAG","")</f>
-        <v>FLAG</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="str">
         <f>IF(A3&lt;&gt;B3,"FLAG","")</f>
@@ -1880,58 +1698,58 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" t="s">
-        <v>252</v>
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <f>IF(A4&lt;&gt;B4,"FLAG","")</f>
-        <v/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I5" t="str">
         <f>IF(A5&lt;&gt;B5,"FLAG","")</f>
@@ -1940,28 +1758,28 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I6" t="str">
         <f>IF(A6&lt;&gt;B6,"FLAG","")</f>
@@ -1970,28 +1788,28 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I7" t="str">
         <f>IF(A7&lt;&gt;B7,"FLAG","")</f>
@@ -2000,28 +1818,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I8" t="str">
         <f>IF(A8&lt;&gt;B8,"FLAG","")</f>
@@ -2030,28 +1848,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I9" t="str">
         <f>IF(A9&lt;&gt;B9,"FLAG","")</f>
@@ -2060,28 +1878,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I10" t="str">
         <f>IF(A10&lt;&gt;B10,"FLAG","")</f>
@@ -2090,28 +1908,28 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I11" t="str">
         <f>IF(A11&lt;&gt;B11,"FLAG","")</f>
@@ -2120,28 +1938,28 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12" t="str">
         <f>IF(A12&lt;&gt;B12,"FLAG","")</f>
@@ -2150,28 +1968,28 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I13" t="str">
         <f>IF(A13&lt;&gt;B13,"FLAG","")</f>
@@ -2180,28 +1998,28 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I14" t="str">
         <f>IF(A14&lt;&gt;B14,"FLAG","")</f>
@@ -2210,28 +2028,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I15" t="str">
         <f>IF(A15&lt;&gt;B15,"FLAG","")</f>
@@ -2240,28 +2058,28 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I16" t="str">
         <f>IF(A16&lt;&gt;B16,"FLAG","")</f>
@@ -2270,28 +2088,28 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I17" t="str">
         <f>IF(A17&lt;&gt;B17,"FLAG","")</f>
@@ -2300,28 +2118,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I18" t="str">
         <f>IF(A18&lt;&gt;B18,"FLAG","")</f>
@@ -2330,28 +2148,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I19" t="str">
         <f>IF(A19&lt;&gt;B19,"FLAG","")</f>
@@ -2360,28 +2178,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
         <f>IF(A20&lt;&gt;B20,"FLAG","")</f>
@@ -2390,28 +2208,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I21" t="str">
         <f>IF(A21&lt;&gt;B21,"FLAG","")</f>
@@ -2420,28 +2238,28 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I22" t="str">
         <f>IF(A22&lt;&gt;B22,"FLAG","")</f>
@@ -2450,28 +2268,28 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I23" t="str">
         <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
@@ -2480,28 +2298,28 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I24" t="str">
         <f>IF(A24&lt;&gt;B24,"FLAG","")</f>
@@ -2510,28 +2328,28 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I25" t="str">
         <f>IF(A25&lt;&gt;B25,"FLAG","")</f>
@@ -2540,28 +2358,28 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I26" t="str">
         <f>IF(A26&lt;&gt;B26,"FLAG","")</f>
@@ -2570,28 +2388,28 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G27" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I27" t="str">
         <f>IF(A27&lt;&gt;B27,"FLAG","")</f>
@@ -2600,28 +2418,28 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I28" t="str">
         <f>IF(A28&lt;&gt;B28,"FLAG","")</f>
@@ -2630,28 +2448,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I29" t="str">
         <f>IF(A29&lt;&gt;B29,"FLAG","")</f>
@@ -2660,28 +2478,28 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I30" t="str">
         <f>IF(A30&lt;&gt;B30,"FLAG","")</f>
@@ -2690,28 +2508,28 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I31" t="str">
         <f>IF(A31&lt;&gt;B31,"FLAG","")</f>
@@ -2720,28 +2538,28 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I32" t="str">
         <f>IF(A32&lt;&gt;B32,"FLAG","")</f>
@@ -2750,28 +2568,28 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I33" t="str">
         <f>IF(A33&lt;&gt;B33,"FLAG","")</f>
@@ -2780,28 +2598,28 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I34" t="str">
         <f>IF(A34&lt;&gt;B34,"FLAG","")</f>
@@ -2810,28 +2628,28 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I35" t="str">
         <f>IF(A35&lt;&gt;B35,"FLAG","")</f>
@@ -2840,88 +2658,88 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I36" t="str">
         <f>IF(A36&lt;&gt;B36,"FLAG","")</f>
-        <v/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G37" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I37" t="str">
         <f>IF(A37&lt;&gt;B37,"FLAG","")</f>
-        <v/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G38" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I38" t="str">
         <f>IF(A38&lt;&gt;B38,"FLAG","")</f>
@@ -2930,28 +2748,28 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="C39" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G39" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I39" t="str">
         <f>IF(A39&lt;&gt;B39,"FLAG","")</f>
@@ -2960,28 +2778,28 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G40" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I40" t="str">
         <f>IF(A40&lt;&gt;B40,"FLAG","")</f>
@@ -2990,58 +2808,58 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I41" t="str">
         <f>IF(A41&lt;&gt;B41,"FLAG","")</f>
-        <v>FLAG</v>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>252</v>
+        <v>71</v>
+      </c>
+      <c r="F42" t="s">
+        <v>195</v>
       </c>
       <c r="G42" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I42" t="str">
         <f>IF(A42&lt;&gt;B42,"FLAG","")</f>
@@ -3050,28 +2868,28 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G43" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I43" t="str">
         <f>IF(A43&lt;&gt;B43,"FLAG","")</f>
@@ -3080,28 +2898,28 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="E44" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G44" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I44" t="str">
         <f>IF(A44&lt;&gt;B44,"FLAG","")</f>
@@ -3110,28 +2928,28 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G45" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I45" t="str">
         <f>IF(A45&lt;&gt;B45,"FLAG","")</f>
@@ -3140,28 +2958,28 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G46" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I46" t="str">
         <f>IF(A46&lt;&gt;B46,"FLAG","")</f>
@@ -3170,28 +2988,28 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G47" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I47" t="str">
         <f>IF(A47&lt;&gt;B47,"FLAG","")</f>
@@ -3200,28 +3018,28 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="E48" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G48" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I48" t="str">
         <f>IF(A48&lt;&gt;B48,"FLAG","")</f>
@@ -3230,28 +3048,28 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C49" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="E49" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G49" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I49" t="str">
         <f>IF(A49&lt;&gt;B49,"FLAG","")</f>
@@ -3260,28 +3078,28 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="C50" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E50" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G50" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I50" t="str">
         <f>IF(A50&lt;&gt;B50,"FLAG","")</f>
@@ -3290,28 +3108,28 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D51" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I51" t="str">
         <f>IF(A51&lt;&gt;B51,"FLAG","")</f>
@@ -3320,28 +3138,28 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D52" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G52" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H52" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I52" t="str">
         <f>IF(A52&lt;&gt;B52,"FLAG","")</f>
@@ -3350,28 +3168,28 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E53" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G53" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H53" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I53" t="str">
         <f>IF(A53&lt;&gt;B53,"FLAG","")</f>
@@ -3380,28 +3198,28 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D54" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G54" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H54" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I54" t="str">
         <f>IF(A54&lt;&gt;B54,"FLAG","")</f>
@@ -3410,28 +3228,28 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G55" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H55" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I55" t="str">
         <f>IF(A55&lt;&gt;B55,"FLAG","")</f>
@@ -3440,28 +3258,28 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D56" t="s">
+        <v>83</v>
+      </c>
+      <c r="E56" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G56" t="s">
         <v>59</v>
       </c>
-      <c r="E56" t="s">
-        <v>59</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G56" t="s">
-        <v>28</v>
-      </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I56" t="str">
         <f>IF(A56&lt;&gt;B56,"FLAG","")</f>
@@ -3470,28 +3288,28 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D57" t="s">
+        <v>83</v>
+      </c>
+      <c r="E57" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G57" t="s">
         <v>59</v>
       </c>
-      <c r="E57" t="s">
-        <v>59</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G57" t="s">
-        <v>28</v>
-      </c>
       <c r="H57" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I57" t="str">
         <f>IF(A57&lt;&gt;B57,"FLAG","")</f>
@@ -3500,28 +3318,28 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" t="s">
+        <v>83</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G58" t="s">
         <v>59</v>
       </c>
-      <c r="E58" t="s">
-        <v>59</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G58" t="s">
-        <v>28</v>
-      </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I58" t="str">
         <f>IF(A58&lt;&gt;B58,"FLAG","")</f>
@@ -3530,28 +3348,28 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C59" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D59" t="s">
+        <v>83</v>
+      </c>
+      <c r="E59" t="s">
+        <v>83</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G59" t="s">
         <v>59</v>
       </c>
-      <c r="E59" t="s">
-        <v>59</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G59" t="s">
-        <v>28</v>
-      </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I59" t="str">
         <f>IF(A59&lt;&gt;B59,"FLAG","")</f>
@@ -3560,28 +3378,28 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D60" t="s">
+        <v>83</v>
+      </c>
+      <c r="E60" t="s">
+        <v>83</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G60" t="s">
         <v>59</v>
       </c>
-      <c r="E60" t="s">
-        <v>59</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G60" t="s">
-        <v>28</v>
-      </c>
       <c r="H60" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I60" t="str">
         <f>IF(A60&lt;&gt;B60,"FLAG","")</f>
@@ -3590,28 +3408,28 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D61" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" t="s">
+        <v>83</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G61" t="s">
         <v>59</v>
       </c>
-      <c r="E61" t="s">
-        <v>59</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G61" t="s">
-        <v>28</v>
-      </c>
       <c r="H61" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I61" t="str">
         <f>IF(A61&lt;&gt;B61,"FLAG","")</f>
@@ -3620,28 +3438,28 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D62" t="s">
+        <v>83</v>
+      </c>
+      <c r="E62" t="s">
+        <v>83</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G62" t="s">
         <v>59</v>
       </c>
-      <c r="E62" t="s">
-        <v>59</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G62" t="s">
-        <v>28</v>
-      </c>
       <c r="H62" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I62" t="str">
         <f>IF(A62&lt;&gt;B62,"FLAG","")</f>
@@ -3650,28 +3468,28 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D63" t="s">
+        <v>83</v>
+      </c>
+      <c r="E63" t="s">
+        <v>83</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G63" t="s">
         <v>59</v>
       </c>
-      <c r="E63" t="s">
-        <v>59</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G63" t="s">
-        <v>28</v>
-      </c>
       <c r="H63" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I63" t="str">
         <f>IF(A63&lt;&gt;B63,"FLAG","")</f>
@@ -3680,28 +3498,28 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D64" t="s">
+        <v>83</v>
+      </c>
+      <c r="E64" t="s">
+        <v>83</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G64" t="s">
         <v>59</v>
       </c>
-      <c r="E64" t="s">
-        <v>59</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G64" t="s">
-        <v>28</v>
-      </c>
       <c r="H64" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I64" t="str">
         <f>IF(A64&lt;&gt;B64,"FLAG","")</f>
@@ -3710,28 +3528,28 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D65" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" t="s">
+        <v>83</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G65" t="s">
         <v>59</v>
       </c>
-      <c r="E65" t="s">
-        <v>59</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G65" t="s">
-        <v>28</v>
-      </c>
       <c r="H65" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I65" t="str">
         <f>IF(A65&lt;&gt;B65,"FLAG","")</f>
@@ -3740,28 +3558,28 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C66" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G66" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I66" t="str">
         <f>IF(A66&lt;&gt;B66,"FLAG","")</f>
@@ -3770,28 +3588,28 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G67" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H67" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I67" t="str">
         <f>IF(A67&lt;&gt;B67,"FLAG","")</f>
@@ -3799,29 +3617,29 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>126</v>
+      <c r="A68" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G68" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H68" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I68" t="str">
         <f>IF(A68&lt;&gt;B68,"FLAG","")</f>
@@ -3829,29 +3647,29 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>127</v>
+      <c r="A69" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C69" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G69" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H69" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I69" t="str">
         <f>IF(A69&lt;&gt;B69,"FLAG","")</f>
@@ -3859,29 +3677,29 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>128</v>
+      <c r="A70" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C70" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D70" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E70" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G70" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H70" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I70" t="str">
         <f>IF(A70&lt;&gt;B70,"FLAG","")</f>
@@ -3889,29 +3707,29 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>69</v>
+      <c r="A71" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="E71" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G71" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H71" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I71" t="str">
         <f>IF(A71&lt;&gt;B71,"FLAG","")</f>
@@ -3919,89 +3737,89 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>86</v>
+      <c r="A72" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C72" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D72" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E72" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G72" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H72" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="I72" t="str">
         <f>IF(A72&lt;&gt;B72,"FLAG","")</f>
-        <v>FLAG</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D73" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E73" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G73" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H73" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="I73" t="str">
         <f>IF(A73&lt;&gt;B73,"FLAG","")</f>
-        <v>FLAG</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C74" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D74" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E74" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G74" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H74" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="I74" t="str">
         <f>IF(A74&lt;&gt;B74,"FLAG","")</f>
@@ -4010,28 +3828,28 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E75" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G75" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H75" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="I75" t="str">
         <f>IF(A75&lt;&gt;B75,"FLAG","")</f>
@@ -4040,28 +3858,28 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C76" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E76" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G76" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H76" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="I76" t="str">
         <f>IF(A76&lt;&gt;B76,"FLAG","")</f>
@@ -4070,28 +3888,28 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C77" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E77" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G77" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H77" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="I77" t="str">
         <f>IF(A77&lt;&gt;B77,"FLAG","")</f>
@@ -4100,28 +3918,28 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C78" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D78" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E78" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G78" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H78" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I78" t="str">
         <f>IF(A78&lt;&gt;B78,"FLAG","")</f>
@@ -4130,28 +3948,28 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D79" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E79" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G79" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H79" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I79" t="str">
         <f>IF(A79&lt;&gt;B79,"FLAG","")</f>
@@ -4160,28 +3978,28 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D80" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E80" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G80" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H80" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I80" t="str">
         <f>IF(A80&lt;&gt;B80,"FLAG","")</f>
@@ -4190,28 +4008,28 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C81" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D81" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E81" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G81" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H81" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I81" t="str">
         <f>IF(A81&lt;&gt;B81,"FLAG","")</f>
@@ -4220,28 +4038,28 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D82" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E82" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G82" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H82" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I82" t="str">
         <f>IF(A82&lt;&gt;B82,"FLAG","")</f>
@@ -4250,28 +4068,28 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C83" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D83" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E83" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G83" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H83" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I83" t="str">
         <f>IF(A83&lt;&gt;B83,"FLAG","")</f>
@@ -4280,28 +4098,28 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B84" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C84" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D84" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E84" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G84" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H84" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I84" t="str">
         <f>IF(A84&lt;&gt;B84,"FLAG","")</f>
@@ -4310,28 +4128,28 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B85" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C85" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D85" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E85" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G85" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H85" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I85" t="str">
         <f>IF(A85&lt;&gt;B85,"FLAG","")</f>
@@ -4340,28 +4158,28 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D86" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E86" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G86" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H86" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I86" t="str">
         <f>IF(A86&lt;&gt;B86,"FLAG","")</f>
@@ -4370,28 +4188,28 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B87" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C87" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E87" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G87" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H87" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I87" t="str">
         <f>IF(A87&lt;&gt;B87,"FLAG","")</f>
@@ -4400,28 +4218,28 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="C88" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E88" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G88" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H88" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I88" t="str">
         <f>IF(A88&lt;&gt;B88,"FLAG","")</f>
@@ -4430,13 +4248,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B89" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C89" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D89" t="s">
         <v>130</v>
@@ -4445,13 +4263,13 @@
         <v>130</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G89" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="H89" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I89" t="str">
         <f>IF(A89&lt;&gt;B89,"FLAG","")</f>
@@ -4460,28 +4278,28 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="B90" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="C90" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D90" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="E90" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G90" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="H90" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I90" t="str">
         <f>IF(A90&lt;&gt;B90,"FLAG","")</f>
@@ -4490,28 +4308,28 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="B91" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="C91" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D91" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="E91" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G91" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="H91" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I91" t="str">
         <f>IF(A91&lt;&gt;B91,"FLAG","")</f>
@@ -4520,28 +4338,28 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="C92" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D92" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="E92" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G92" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="H92" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I92" t="str">
         <f>IF(A92&lt;&gt;B92,"FLAG","")</f>
@@ -4550,28 +4368,28 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B93" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="C93" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D93" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="E93" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G93" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="H93" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I93" t="str">
         <f>IF(A93&lt;&gt;B93,"FLAG","")</f>
@@ -4580,28 +4398,28 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C94" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D94" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="E94" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G94" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="H94" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I94" t="str">
         <f>IF(A94&lt;&gt;B94,"FLAG","")</f>
@@ -4610,28 +4428,28 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B95" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D95" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E95" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G95" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="H95" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I95" t="str">
         <f>IF(A95&lt;&gt;B95,"FLAG","")</f>
@@ -4640,28 +4458,28 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C96" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E96" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G96" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="H96" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I96" t="str">
         <f>IF(A96&lt;&gt;B96,"FLAG","")</f>
@@ -4670,28 +4488,28 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C97" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E97" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G97" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="H97" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I97" t="str">
         <f>IF(A97&lt;&gt;B97,"FLAG","")</f>
@@ -4700,28 +4518,28 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C98" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D98" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E98" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G98" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="H98" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I98" t="str">
         <f>IF(A98&lt;&gt;B98,"FLAG","")</f>
@@ -4730,28 +4548,28 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="C99" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D99" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E99" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G99" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="H99" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I99" t="str">
         <f>IF(A99&lt;&gt;B99,"FLAG","")</f>
@@ -4760,28 +4578,28 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B100" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C100" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D100" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="E100" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G100" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="H100" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I100" t="str">
         <f>IF(A100&lt;&gt;B100,"FLAG","")</f>
@@ -4790,28 +4608,28 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="C101" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="E101" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G101" t="s">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="H101" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I101" t="str">
         <f>IF(A101&lt;&gt;B101,"FLAG","")</f>
@@ -4820,28 +4638,28 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B102" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C102" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D102" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="E102" t="s">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G102" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H102" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I102" t="str">
         <f>IF(A102&lt;&gt;B102,"FLAG","")</f>
@@ -4850,28 +4668,28 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B103" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C103" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D103" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="E103" t="s">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G103" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H103" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I103" t="str">
         <f>IF(A103&lt;&gt;B103,"FLAG","")</f>
@@ -4880,28 +4698,28 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B104" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C104" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D104" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E104" t="s">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G104" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H104" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I104" t="str">
         <f>IF(A104&lt;&gt;B104,"FLAG","")</f>
@@ -4910,28 +4728,28 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B105" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C105" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D105" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E105" t="s">
-        <v>258</v>
+        <v>150</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G105" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H105" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I105" t="str">
         <f>IF(A105&lt;&gt;B105,"FLAG","")</f>
@@ -4940,58 +4758,58 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>264</v>
+        <v>153</v>
       </c>
       <c r="B106" t="s">
-        <v>264</v>
+        <v>154</v>
       </c>
       <c r="C106" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D106" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="E106" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G106" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H106" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I106" t="str">
         <f>IF(A106&lt;&gt;B106,"FLAG","")</f>
-        <v/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B107" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C107" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D107" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="E107" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G107" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H107" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I107" t="str">
         <f>IF(A107&lt;&gt;B107,"FLAG","")</f>
@@ -5000,28 +4818,28 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B108" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C108" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D108" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="E108" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G108" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H108" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I108" t="str">
         <f>IF(A108&lt;&gt;B108,"FLAG","")</f>
@@ -5030,28 +4848,28 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B109" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C109" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D109" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="E109" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G109" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H109" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I109" t="str">
         <f>IF(A109&lt;&gt;B109,"FLAG","")</f>
@@ -5060,54 +4878,58 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B110" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C110" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D110" t="s">
-        <v>160</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>258</v>
+        <v>199</v>
+      </c>
+      <c r="E110" t="s">
+        <v>199</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G110" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H110" t="s">
-        <v>154</v>
+        <v>4</v>
+      </c>
+      <c r="I110" t="str">
+        <f>IF(A110&lt;&gt;B110,"FLAG","")</f>
+        <v/>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B111" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C111" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D111" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="E111" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G111" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H111" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I111" t="str">
         <f>IF(A111&lt;&gt;B111,"FLAG","")</f>
@@ -5116,28 +4938,28 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B112" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C112" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D112" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="E112" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G112" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H112" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I112" t="str">
         <f>IF(A112&lt;&gt;B112,"FLAG","")</f>
@@ -5146,28 +4968,28 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B113" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C113" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D113" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="E113" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G113" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H113" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I113" t="str">
         <f>IF(A113&lt;&gt;B113,"FLAG","")</f>
@@ -5182,22 +5004,22 @@
         <v>165</v>
       </c>
       <c r="C114" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D114" t="s">
         <v>166</v>
       </c>
       <c r="E114" t="s">
-        <v>259</v>
+        <v>166</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G114" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H114" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I114" t="str">
         <f>IF(A114&lt;&gt;B114,"FLAG","")</f>
@@ -5206,28 +5028,28 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B115" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C115" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D115" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="E115" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G115" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H115" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I115" t="str">
         <f>IF(A115&lt;&gt;B115,"FLAG","")</f>
@@ -5236,28 +5058,28 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B116" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C116" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D116" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="E116" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G116" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H116" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I116" t="str">
         <f>IF(A116&lt;&gt;B116,"FLAG","")</f>
@@ -5266,28 +5088,28 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B117" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C117" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D117" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E117" t="s">
-        <v>261</v>
+        <v>170</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G117" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H117" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I117" t="str">
         <f>IF(A117&lt;&gt;B117,"FLAG","")</f>
@@ -5296,28 +5118,28 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B118" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C118" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D118" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E118" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G118" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H118" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I118" t="str">
         <f>IF(A118&lt;&gt;B118,"FLAG","")</f>
@@ -5326,28 +5148,28 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B119" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C119" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D119" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E119" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G119" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H119" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I119" t="str">
         <f>IF(A119&lt;&gt;B119,"FLAG","")</f>
@@ -5356,1033 +5178,44 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B120" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C120" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="D120" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E120" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G120" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="H120" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="I120" t="str">
         <f>IF(A120&lt;&gt;B120,"FLAG","")</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>179</v>
-      </c>
-      <c r="B121" t="s">
-        <v>179</v>
-      </c>
-      <c r="C121" t="s">
-        <v>248</v>
-      </c>
-      <c r="D121" t="s">
-        <v>180</v>
-      </c>
-      <c r="E121" t="s">
-        <v>263</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G121" t="s">
-        <v>152</v>
-      </c>
-      <c r="H121" t="s">
-        <v>154</v>
-      </c>
-      <c r="I121" t="str">
-        <f>IF(A121&lt;&gt;B121,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>182</v>
-      </c>
-      <c r="B122" t="s">
-        <v>182</v>
-      </c>
-      <c r="C122" t="s">
-        <v>249</v>
-      </c>
-      <c r="D122" t="s">
-        <v>184</v>
-      </c>
-      <c r="E122" t="s">
-        <v>184</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G122" t="s">
-        <v>183</v>
-      </c>
-      <c r="H122" t="s">
-        <v>17</v>
-      </c>
-      <c r="I122" t="str">
-        <f>IF(A122&lt;&gt;B122,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>185</v>
-      </c>
-      <c r="B123" t="s">
-        <v>185</v>
-      </c>
-      <c r="C123" t="s">
-        <v>249</v>
-      </c>
-      <c r="D123" t="s">
-        <v>186</v>
-      </c>
-      <c r="E123" t="s">
-        <v>186</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G123" t="s">
-        <v>183</v>
-      </c>
-      <c r="H123" t="s">
-        <v>17</v>
-      </c>
-      <c r="I123" t="str">
-        <f>IF(A123&lt;&gt;B123,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>187</v>
-      </c>
-      <c r="B124" t="s">
-        <v>187</v>
-      </c>
-      <c r="C124" t="s">
-        <v>249</v>
-      </c>
-      <c r="D124" t="s">
-        <v>188</v>
-      </c>
-      <c r="E124" t="s">
-        <v>188</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G124" t="s">
-        <v>183</v>
-      </c>
-      <c r="H124" t="s">
-        <v>17</v>
-      </c>
-      <c r="I124" t="str">
-        <f>IF(A124&lt;&gt;B124,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>189</v>
-      </c>
-      <c r="B125" t="s">
-        <v>189</v>
-      </c>
-      <c r="C125" t="s">
-        <v>249</v>
-      </c>
-      <c r="D125" t="s">
-        <v>190</v>
-      </c>
-      <c r="E125" t="s">
-        <v>190</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G125" t="s">
-        <v>183</v>
-      </c>
-      <c r="H125" t="s">
-        <v>17</v>
-      </c>
-      <c r="I125" t="str">
-        <f>IF(A125&lt;&gt;B125,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>191</v>
-      </c>
-      <c r="B126" t="s">
-        <v>191</v>
-      </c>
-      <c r="C126" t="s">
-        <v>249</v>
-      </c>
-      <c r="D126" t="s">
-        <v>190</v>
-      </c>
-      <c r="E126" t="s">
-        <v>190</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G126" t="s">
-        <v>183</v>
-      </c>
-      <c r="H126" t="s">
-        <v>17</v>
-      </c>
-      <c r="I126" t="str">
-        <f>IF(A126&lt;&gt;B126,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
-        <v>192</v>
-      </c>
-      <c r="B127" t="s">
-        <v>192</v>
-      </c>
-      <c r="C127" t="s">
-        <v>249</v>
-      </c>
-      <c r="D127" t="s">
-        <v>190</v>
-      </c>
-      <c r="E127" t="s">
-        <v>190</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G127" t="s">
-        <v>183</v>
-      </c>
-      <c r="H127" t="s">
-        <v>17</v>
-      </c>
-      <c r="I127" t="str">
-        <f>IF(A127&lt;&gt;B127,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
-        <v>193</v>
-      </c>
-      <c r="B128" t="s">
-        <v>193</v>
-      </c>
-      <c r="C128" t="s">
-        <v>249</v>
-      </c>
-      <c r="D128" t="s">
-        <v>190</v>
-      </c>
-      <c r="E128" t="s">
-        <v>190</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G128" t="s">
-        <v>183</v>
-      </c>
-      <c r="H128" t="s">
-        <v>17</v>
-      </c>
-      <c r="I128" t="str">
-        <f>IF(A128&lt;&gt;B128,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>194</v>
-      </c>
-      <c r="B129" t="s">
-        <v>194</v>
-      </c>
-      <c r="C129" t="s">
-        <v>249</v>
-      </c>
-      <c r="D129" t="s">
-        <v>190</v>
-      </c>
-      <c r="E129" t="s">
-        <v>190</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G129" t="s">
-        <v>183</v>
-      </c>
-      <c r="H129" t="s">
-        <v>17</v>
-      </c>
-      <c r="I129" t="str">
-        <f>IF(A129&lt;&gt;B129,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>195</v>
-      </c>
-      <c r="B130" t="s">
-        <v>195</v>
-      </c>
-      <c r="C130" t="s">
-        <v>249</v>
-      </c>
-      <c r="D130" t="s">
-        <v>190</v>
-      </c>
-      <c r="E130" t="s">
-        <v>190</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G130" t="s">
-        <v>183</v>
-      </c>
-      <c r="H130" t="s">
-        <v>17</v>
-      </c>
-      <c r="I130" t="str">
-        <f>IF(A130&lt;&gt;B130,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
-        <v>196</v>
-      </c>
-      <c r="B131" t="s">
-        <v>196</v>
-      </c>
-      <c r="C131" t="s">
-        <v>249</v>
-      </c>
-      <c r="D131" t="s">
-        <v>190</v>
-      </c>
-      <c r="E131" t="s">
-        <v>190</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G131" t="s">
-        <v>183</v>
-      </c>
-      <c r="H131" t="s">
-        <v>17</v>
-      </c>
-      <c r="I131" t="str">
-        <f>IF(A131&lt;&gt;B131,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>197</v>
-      </c>
-      <c r="B132" t="s">
-        <v>197</v>
-      </c>
-      <c r="C132" t="s">
-        <v>249</v>
-      </c>
-      <c r="D132" t="s">
-        <v>190</v>
-      </c>
-      <c r="E132" t="s">
-        <v>190</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G132" t="s">
-        <v>183</v>
-      </c>
-      <c r="H132" t="s">
-        <v>17</v>
-      </c>
-      <c r="I132" t="str">
-        <f>IF(A132&lt;&gt;B132,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>198</v>
-      </c>
-      <c r="B133" t="s">
-        <v>198</v>
-      </c>
-      <c r="C133" t="s">
-        <v>249</v>
-      </c>
-      <c r="D133" t="s">
-        <v>190</v>
-      </c>
-      <c r="E133" t="s">
-        <v>190</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G133" t="s">
-        <v>183</v>
-      </c>
-      <c r="H133" t="s">
-        <v>17</v>
-      </c>
-      <c r="I133" t="str">
-        <f>IF(A133&lt;&gt;B133,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>199</v>
-      </c>
-      <c r="B134" t="s">
-        <v>199</v>
-      </c>
-      <c r="C134" t="s">
-        <v>249</v>
-      </c>
-      <c r="D134" t="s">
-        <v>190</v>
-      </c>
-      <c r="E134" t="s">
-        <v>190</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G134" t="s">
-        <v>183</v>
-      </c>
-      <c r="H134" t="s">
-        <v>17</v>
-      </c>
-      <c r="I134" t="str">
-        <f>IF(A134&lt;&gt;B134,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>200</v>
-      </c>
-      <c r="B135" t="s">
-        <v>200</v>
-      </c>
-      <c r="C135" t="s">
-        <v>249</v>
-      </c>
-      <c r="D135" t="s">
-        <v>190</v>
-      </c>
-      <c r="E135" t="s">
-        <v>190</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G135" t="s">
-        <v>183</v>
-      </c>
-      <c r="H135" t="s">
-        <v>17</v>
-      </c>
-      <c r="I135" t="str">
-        <f>IF(A135&lt;&gt;B135,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>201</v>
-      </c>
-      <c r="B136" t="s">
-        <v>201</v>
-      </c>
-      <c r="C136" t="s">
-        <v>249</v>
-      </c>
-      <c r="D136" t="s">
-        <v>190</v>
-      </c>
-      <c r="E136" t="s">
-        <v>190</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G136" t="s">
-        <v>183</v>
-      </c>
-      <c r="H136" t="s">
-        <v>17</v>
-      </c>
-      <c r="I136" t="str">
-        <f>IF(A136&lt;&gt;B136,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>202</v>
-      </c>
-      <c r="B137" t="s">
-        <v>202</v>
-      </c>
-      <c r="C137" t="s">
-        <v>249</v>
-      </c>
-      <c r="D137" t="s">
-        <v>190</v>
-      </c>
-      <c r="E137" t="s">
-        <v>190</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G137" t="s">
-        <v>183</v>
-      </c>
-      <c r="H137" t="s">
-        <v>17</v>
-      </c>
-      <c r="I137" t="str">
-        <f>IF(A137&lt;&gt;B137,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>203</v>
-      </c>
-      <c r="B138" t="s">
-        <v>203</v>
-      </c>
-      <c r="C138" t="s">
-        <v>249</v>
-      </c>
-      <c r="D138" t="s">
-        <v>204</v>
-      </c>
-      <c r="E138" t="s">
-        <v>204</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G138" t="s">
-        <v>183</v>
-      </c>
-      <c r="H138" t="s">
-        <v>17</v>
-      </c>
-      <c r="I138" t="str">
-        <f>IF(A138&lt;&gt;B138,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>207</v>
-      </c>
-      <c r="B139" t="s">
-        <v>208</v>
-      </c>
-      <c r="C139" t="s">
-        <v>249</v>
-      </c>
-      <c r="D139" t="s">
-        <v>207</v>
-      </c>
-      <c r="E139" t="s">
-        <v>207</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G139" t="s">
-        <v>183</v>
-      </c>
-      <c r="H139" t="s">
-        <v>17</v>
-      </c>
-      <c r="I139" t="str">
-        <f>IF(A139&lt;&gt;B139,"FLAG","")</f>
-        <v>FLAG</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>211</v>
-      </c>
-      <c r="B140" t="s">
-        <v>212</v>
-      </c>
-      <c r="C140" t="s">
-        <v>249</v>
-      </c>
-      <c r="D140" t="s">
-        <v>210</v>
-      </c>
-      <c r="E140" t="s">
-        <v>210</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G140" t="s">
-        <v>183</v>
-      </c>
-      <c r="H140" t="s">
-        <v>17</v>
-      </c>
-      <c r="I140" t="str">
-        <f>IF(A140&lt;&gt;B140,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>209</v>
-      </c>
-      <c r="B141" t="s">
-        <v>209</v>
-      </c>
-      <c r="C141" t="s">
-        <v>249</v>
-      </c>
-      <c r="D141" t="s">
-        <v>210</v>
-      </c>
-      <c r="E141" t="s">
-        <v>210</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G141" t="s">
-        <v>183</v>
-      </c>
-      <c r="H141" t="s">
-        <v>17</v>
-      </c>
-      <c r="I141" t="str">
-        <f>IF(A141&lt;&gt;B141,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>213</v>
-      </c>
-      <c r="B142" t="s">
-        <v>214</v>
-      </c>
-      <c r="C142" t="s">
-        <v>249</v>
-      </c>
-      <c r="D142" t="s">
-        <v>210</v>
-      </c>
-      <c r="E142" t="s">
-        <v>210</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G142" t="s">
-        <v>183</v>
-      </c>
-      <c r="H142" t="s">
-        <v>17</v>
-      </c>
-      <c r="I142" t="str">
-        <f>IF(A142&lt;&gt;B142,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>215</v>
-      </c>
-      <c r="B143" t="s">
-        <v>216</v>
-      </c>
-      <c r="C143" t="s">
-        <v>249</v>
-      </c>
-      <c r="D143" t="s">
-        <v>210</v>
-      </c>
-      <c r="E143" t="s">
-        <v>210</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G143" t="s">
-        <v>183</v>
-      </c>
-      <c r="H143" t="s">
-        <v>17</v>
-      </c>
-      <c r="I143" t="str">
-        <f>IF(A143&lt;&gt;B143,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>217</v>
-      </c>
-      <c r="B144" t="s">
-        <v>217</v>
-      </c>
-      <c r="C144" t="s">
-        <v>249</v>
-      </c>
-      <c r="D144" t="s">
-        <v>218</v>
-      </c>
-      <c r="E144" t="s">
-        <v>218</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G144" t="s">
-        <v>183</v>
-      </c>
-      <c r="H144" t="s">
-        <v>17</v>
-      </c>
-      <c r="I144" t="str">
-        <f>IF(A144&lt;&gt;B144,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>219</v>
-      </c>
-      <c r="B145" t="s">
-        <v>219</v>
-      </c>
-      <c r="C145" t="s">
-        <v>249</v>
-      </c>
-      <c r="D145" t="s">
-        <v>218</v>
-      </c>
-      <c r="E145" t="s">
-        <v>218</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G145" t="s">
-        <v>183</v>
-      </c>
-      <c r="H145" t="s">
-        <v>17</v>
-      </c>
-      <c r="I145" t="str">
-        <f>IF(A145&lt;&gt;B145,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>220</v>
-      </c>
-      <c r="B146" t="s">
-        <v>220</v>
-      </c>
-      <c r="C146" t="s">
-        <v>249</v>
-      </c>
-      <c r="D146" t="s">
-        <v>218</v>
-      </c>
-      <c r="E146" t="s">
-        <v>218</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G146" t="s">
-        <v>183</v>
-      </c>
-      <c r="H146" t="s">
-        <v>17</v>
-      </c>
-      <c r="I146" t="str">
-        <f>IF(A146&lt;&gt;B146,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>221</v>
-      </c>
-      <c r="B147" t="s">
-        <v>221</v>
-      </c>
-      <c r="C147" t="s">
-        <v>249</v>
-      </c>
-      <c r="D147" t="s">
-        <v>222</v>
-      </c>
-      <c r="E147" t="s">
-        <v>222</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G147" t="s">
-        <v>183</v>
-      </c>
-      <c r="H147" t="s">
-        <v>17</v>
-      </c>
-      <c r="I147" t="str">
-        <f>IF(A147&lt;&gt;B147,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>223</v>
-      </c>
-      <c r="B148" t="s">
-        <v>223</v>
-      </c>
-      <c r="C148" t="s">
-        <v>249</v>
-      </c>
-      <c r="D148" t="s">
-        <v>223</v>
-      </c>
-      <c r="E148" t="s">
-        <v>223</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G148" t="s">
-        <v>183</v>
-      </c>
-      <c r="H148" t="s">
-        <v>17</v>
-      </c>
-      <c r="I148" t="str">
-        <f>IF(A148&lt;&gt;B148,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>224</v>
-      </c>
-      <c r="B149" t="s">
-        <v>224</v>
-      </c>
-      <c r="C149" t="s">
-        <v>249</v>
-      </c>
-      <c r="D149" t="s">
-        <v>223</v>
-      </c>
-      <c r="E149" t="s">
-        <v>223</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G149" t="s">
-        <v>183</v>
-      </c>
-      <c r="H149" t="s">
-        <v>17</v>
-      </c>
-      <c r="I149" t="str">
-        <f>IF(A149&lt;&gt;B149,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>225</v>
-      </c>
-      <c r="B150" t="s">
-        <v>225</v>
-      </c>
-      <c r="C150" t="s">
-        <v>249</v>
-      </c>
-      <c r="D150" t="s">
-        <v>226</v>
-      </c>
-      <c r="E150" t="s">
-        <v>226</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G150" t="s">
-        <v>183</v>
-      </c>
-      <c r="H150" t="s">
-        <v>17</v>
-      </c>
-      <c r="I150" t="str">
-        <f>IF(A150&lt;&gt;B150,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>227</v>
-      </c>
-      <c r="B151" t="s">
-        <v>227</v>
-      </c>
-      <c r="C151" t="s">
-        <v>249</v>
-      </c>
-      <c r="D151" t="s">
-        <v>226</v>
-      </c>
-      <c r="E151" t="s">
-        <v>226</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G151" t="s">
-        <v>183</v>
-      </c>
-      <c r="H151" t="s">
-        <v>17</v>
-      </c>
-      <c r="I151" t="str">
-        <f>IF(A151&lt;&gt;B151,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
-        <v>228</v>
-      </c>
-      <c r="B152" t="s">
-        <v>228</v>
-      </c>
-      <c r="C152" t="s">
-        <v>249</v>
-      </c>
-      <c r="D152" t="s">
-        <v>226</v>
-      </c>
-      <c r="E152" t="s">
-        <v>226</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G152" t="s">
-        <v>183</v>
-      </c>
-      <c r="H152" t="s">
-        <v>17</v>
-      </c>
-      <c r="I152" t="str">
-        <f>IF(A152&lt;&gt;B152,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>229</v>
-      </c>
-      <c r="B153" t="s">
-        <v>229</v>
-      </c>
-      <c r="C153" t="s">
-        <v>249</v>
-      </c>
-      <c r="D153" t="s">
-        <v>230</v>
-      </c>
-      <c r="E153" t="s">
-        <v>230</v>
-      </c>
-      <c r="F153" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G153" t="s">
-        <v>183</v>
-      </c>
-      <c r="H153" t="s">
-        <v>17</v>
-      </c>
-      <c r="I153" t="str">
-        <f>IF(A153&lt;&gt;B153,"FLAG","")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I153">
-    <sortCondition ref="F2:F153"/>
-    <sortCondition ref="C2:C153"/>
-    <sortCondition ref="E2:E153"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
+    <sortCondition ref="C2:C120"/>
+    <sortCondition ref="G2:G120"/>
+    <sortCondition ref="H2:H120"/>
   </sortState>
-  <conditionalFormatting sqref="I150:I151">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I150)))</formula>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="I117:I118">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I117)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -6395,9 +5228,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I148:I149">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I148)))</formula>
+  <conditionalFormatting sqref="I115:I116">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I115)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -6410,26 +5243,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I107:I147 I2:I105">
-    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="FLAG">
+  <conditionalFormatting sqref="I2:I114">
+    <cfRule type="containsText" dxfId="0" priority="31" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I106">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I106)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6457,16 +5275,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -6475,33 +5293,33 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I2" t="str">
         <f t="shared" ref="I2:I15" si="0">IF(A2&lt;&gt;B2,"FLAG","")</f>
@@ -6510,28 +5328,28 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" si="0"/>
@@ -6540,28 +5358,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="0"/>
@@ -6570,28 +5388,28 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="0"/>
@@ -6600,28 +5418,28 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="0"/>
@@ -6630,28 +5448,28 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
@@ -6660,28 +5478,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="0"/>
@@ -6690,28 +5508,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="0"/>
@@ -6720,28 +5538,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="0"/>
@@ -6750,28 +5568,28 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="0"/>
@@ -6780,28 +5598,28 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="0"/>
@@ -6810,28 +5628,28 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="B13" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="0"/>
@@ -6840,28 +5658,28 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="0"/>
@@ -6870,28 +5688,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="0"/>
@@ -6900,80 +5718,80 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="C16" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I18" t="str">
         <f>IF(A18&lt;&gt;B18,"FLAG","")</f>
@@ -6982,28 +5800,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I19" t="str">
         <f>IF(A19&lt;&gt;B19,"FLAG","")</f>
@@ -7012,28 +5830,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
         <f>IF(A20&lt;&gt;B20,"FLAG","")</f>
@@ -7042,28 +5860,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I21" t="str">
         <f>IF(A21&lt;&gt;B21,"FLAG","")</f>
@@ -7072,28 +5890,28 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="F22" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I22" t="str" cm="1">
         <f t="array" ref="I22">IF(A22&lt;&gt;B22,Changed,"")</f>
@@ -7102,28 +5920,28 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="D23" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I23" t="str">
         <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
@@ -7132,7 +5950,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -7147,7 +5965,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">

--- a/tabular/reference/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/reference/herv_sublineage_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2853C645-5490-4545-BDFB-EEBFB6185980}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4404761-373A-A34C-9F76-40382190E543}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="500" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1662,7 +1662,7 @@
         <v>4</v>
       </c>
       <c r="I2" t="str">
-        <f>IF(A2&lt;&gt;B2,"FLAG","")</f>
+        <f t="shared" ref="I2:I33" si="0">IF(A2&lt;&gt;B2,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="str">
-        <f>IF(A3&lt;&gt;B3,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
         <v>4</v>
       </c>
       <c r="I4" t="str">
-        <f>IF(A4&lt;&gt;B4,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v>FLAG</v>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="str">
-        <f>IF(A5&lt;&gt;B5,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="str">
-        <f>IF(A6&lt;&gt;B6,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="str">
-        <f>IF(A7&lt;&gt;B7,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
         <v>4</v>
       </c>
       <c r="I8" t="str">
-        <f>IF(A8&lt;&gt;B8,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
         <v>4</v>
       </c>
       <c r="I9" t="str">
-        <f>IF(A9&lt;&gt;B9,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="str">
-        <f>IF(A10&lt;&gt;B10,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="str">
-        <f>IF(A11&lt;&gt;B11,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="str">
-        <f>IF(A12&lt;&gt;B12,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="str">
-        <f>IF(A13&lt;&gt;B13,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="str">
-        <f>IF(A14&lt;&gt;B14,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
         <v>4</v>
       </c>
       <c r="I15" t="str">
-        <f>IF(A15&lt;&gt;B15,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="str">
-        <f>IF(A16&lt;&gt;B16,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="str">
-        <f>IF(A17&lt;&gt;B17,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="str">
-        <f>IF(A18&lt;&gt;B18,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="str">
-        <f>IF(A19&lt;&gt;B19,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="str">
-        <f>IF(A20&lt;&gt;B20,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
         <v>4</v>
       </c>
       <c r="I21" t="str">
-        <f>IF(A21&lt;&gt;B21,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         <v>4</v>
       </c>
       <c r="I22" t="str">
-        <f>IF(A22&lt;&gt;B22,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
         <v>4</v>
       </c>
       <c r="I23" t="str">
-        <f>IF(A23&lt;&gt;B23,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="str">
-        <f>IF(A24&lt;&gt;B24,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
         <v>4</v>
       </c>
       <c r="I25" t="str">
-        <f>IF(A25&lt;&gt;B25,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="str">
-        <f>IF(A26&lt;&gt;B26,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="str">
-        <f>IF(A27&lt;&gt;B27,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
         <v>4</v>
       </c>
       <c r="I28" t="str">
-        <f>IF(A28&lt;&gt;B28,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
         <v>4</v>
       </c>
       <c r="I29" t="str">
-        <f>IF(A29&lt;&gt;B29,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
         <v>4</v>
       </c>
       <c r="I30" t="str">
-        <f>IF(A30&lt;&gt;B30,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <f>IF(A31&lt;&gt;B31,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="str">
-        <f>IF(A32&lt;&gt;B32,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <f>IF(A33&lt;&gt;B33,"FLAG","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <f>IF(A34&lt;&gt;B34,"FLAG","")</f>
+        <f t="shared" ref="I34:I65" si="1">IF(A34&lt;&gt;B34,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         <v>4</v>
       </c>
       <c r="I35" t="str">
-        <f>IF(A35&lt;&gt;B35,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
         <v>60</v>
       </c>
       <c r="I36" t="str">
-        <f>IF(A36&lt;&gt;B36,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v>FLAG</v>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>60</v>
       </c>
       <c r="I37" t="str">
-        <f>IF(A37&lt;&gt;B37,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v>FLAG</v>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>60</v>
       </c>
       <c r="I38" t="str">
-        <f>IF(A38&lt;&gt;B38,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
         <v>60</v>
       </c>
       <c r="I39" t="str">
-        <f>IF(A39&lt;&gt;B39,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
         <v>60</v>
       </c>
       <c r="I40" t="str">
-        <f>IF(A40&lt;&gt;B40,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
         <v>60</v>
       </c>
       <c r="I41" t="str">
-        <f>IF(A41&lt;&gt;B41,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
         <v>4</v>
       </c>
       <c r="I42" t="str">
-        <f>IF(A42&lt;&gt;B42,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>4</v>
       </c>
       <c r="I43" t="str">
-        <f>IF(A43&lt;&gt;B43,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
         <v>4</v>
       </c>
       <c r="I44" t="str">
-        <f>IF(A44&lt;&gt;B44,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
         <v>4</v>
       </c>
       <c r="I45" t="str">
-        <f>IF(A45&lt;&gt;B45,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
         <v>4</v>
       </c>
       <c r="I46" t="str">
-        <f>IF(A46&lt;&gt;B46,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
         <v>4</v>
       </c>
       <c r="I47" t="str">
-        <f>IF(A47&lt;&gt;B47,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
         <v>4</v>
       </c>
       <c r="I48" t="str">
-        <f>IF(A48&lt;&gt;B48,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>4</v>
       </c>
       <c r="I49" t="str">
-        <f>IF(A49&lt;&gt;B49,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
         <v>4</v>
       </c>
       <c r="I50" t="str">
-        <f>IF(A50&lt;&gt;B50,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
         <v>4</v>
       </c>
       <c r="I51" t="str">
-        <f>IF(A51&lt;&gt;B51,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
         <v>4</v>
       </c>
       <c r="I52" t="str">
-        <f>IF(A52&lt;&gt;B52,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
         <v>4</v>
       </c>
       <c r="I53" t="str">
-        <f>IF(A53&lt;&gt;B53,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
         <v>4</v>
       </c>
       <c r="I54" t="str">
-        <f>IF(A54&lt;&gt;B54,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
         <v>4</v>
       </c>
       <c r="I55" t="str">
-        <f>IF(A55&lt;&gt;B55,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>4</v>
       </c>
       <c r="I56" t="str">
-        <f>IF(A56&lt;&gt;B56,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>4</v>
       </c>
       <c r="I57" t="str">
-        <f>IF(A57&lt;&gt;B57,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         <v>4</v>
       </c>
       <c r="I58" t="str">
-        <f>IF(A58&lt;&gt;B58,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
         <v>4</v>
       </c>
       <c r="I59" t="str">
-        <f>IF(A59&lt;&gt;B59,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
         <v>4</v>
       </c>
       <c r="I60" t="str">
-        <f>IF(A60&lt;&gt;B60,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
         <v>4</v>
       </c>
       <c r="I61" t="str">
-        <f>IF(A61&lt;&gt;B61,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
         <v>4</v>
       </c>
       <c r="I62" t="str">
-        <f>IF(A62&lt;&gt;B62,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
         <v>4</v>
       </c>
       <c r="I63" t="str">
-        <f>IF(A63&lt;&gt;B63,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
         <v>4</v>
       </c>
       <c r="I64" t="str">
-        <f>IF(A64&lt;&gt;B64,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
         <v>4</v>
       </c>
       <c r="I65" t="str">
-        <f>IF(A65&lt;&gt;B65,"FLAG","")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
         <v>4</v>
       </c>
       <c r="I66" t="str">
-        <f>IF(A66&lt;&gt;B66,"FLAG","")</f>
+        <f t="shared" ref="I66:I97" si="2">IF(A66&lt;&gt;B66,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
         <v>4</v>
       </c>
       <c r="I67" t="str">
-        <f>IF(A67&lt;&gt;B67,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
         <v>4</v>
       </c>
       <c r="I68" t="str">
-        <f>IF(A68&lt;&gt;B68,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
         <v>4</v>
       </c>
       <c r="I69" t="str">
-        <f>IF(A69&lt;&gt;B69,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
         <v>4</v>
       </c>
       <c r="I70" t="str">
-        <f>IF(A70&lt;&gt;B70,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
         <v>4</v>
       </c>
       <c r="I71" t="str">
-        <f>IF(A71&lt;&gt;B71,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
         <v>4</v>
       </c>
       <c r="I72" t="str">
-        <f>IF(A72&lt;&gt;B72,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
         <v>4</v>
       </c>
       <c r="I73" t="str">
-        <f>IF(A73&lt;&gt;B73,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
         <v>4</v>
       </c>
       <c r="I74" t="str">
-        <f>IF(A74&lt;&gt;B74,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
         <v>4</v>
       </c>
       <c r="I75" t="str">
-        <f>IF(A75&lt;&gt;B75,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
         <v>4</v>
       </c>
       <c r="I76" t="str">
-        <f>IF(A76&lt;&gt;B76,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
         <v>4</v>
       </c>
       <c r="I77" t="str">
-        <f>IF(A77&lt;&gt;B77,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
         <v>4</v>
       </c>
       <c r="I78" t="str">
-        <f>IF(A78&lt;&gt;B78,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="I79" t="str">
-        <f>IF(A79&lt;&gt;B79,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="I80" t="str">
-        <f>IF(A80&lt;&gt;B80,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
         <v>4</v>
       </c>
       <c r="I81" t="str">
-        <f>IF(A81&lt;&gt;B81,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
         <v>4</v>
       </c>
       <c r="I82" t="str">
-        <f>IF(A82&lt;&gt;B82,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
         <v>4</v>
       </c>
       <c r="I83" t="str">
-        <f>IF(A83&lt;&gt;B83,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
         <v>4</v>
       </c>
       <c r="I84" t="str">
-        <f>IF(A84&lt;&gt;B84,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
         <v>4</v>
       </c>
       <c r="I85" t="str">
-        <f>IF(A85&lt;&gt;B85,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
         <v>4</v>
       </c>
       <c r="I86" t="str">
-        <f>IF(A86&lt;&gt;B86,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
         <v>4</v>
       </c>
       <c r="I87" t="str">
-        <f>IF(A87&lt;&gt;B87,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
         <v>4</v>
       </c>
       <c r="I88" t="str">
-        <f>IF(A88&lt;&gt;B88,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
         <v>4</v>
       </c>
       <c r="I89" t="str">
-        <f>IF(A89&lt;&gt;B89,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="I90" t="str">
-        <f>IF(A90&lt;&gt;B90,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
         <v>4</v>
       </c>
       <c r="I91" t="str">
-        <f>IF(A91&lt;&gt;B91,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
         <v>4</v>
       </c>
       <c r="I92" t="str">
-        <f>IF(A92&lt;&gt;B92,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
         <v>4</v>
       </c>
       <c r="I93" t="str">
-        <f>IF(A93&lt;&gt;B93,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>4</v>
       </c>
       <c r="I94" t="str">
-        <f>IF(A94&lt;&gt;B94,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>4</v>
       </c>
       <c r="I95" t="str">
-        <f>IF(A95&lt;&gt;B95,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
         <v>4</v>
       </c>
       <c r="I96" t="str">
-        <f>IF(A96&lt;&gt;B96,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
         <v>4</v>
       </c>
       <c r="I97" t="str">
-        <f>IF(A97&lt;&gt;B97,"FLAG","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
         <v>4</v>
       </c>
       <c r="I98" t="str">
-        <f>IF(A98&lt;&gt;B98,"FLAG","")</f>
+        <f t="shared" ref="I98:I120" si="3">IF(A98&lt;&gt;B98,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
         <v>4</v>
       </c>
       <c r="I99" t="str">
-        <f>IF(A99&lt;&gt;B99,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
         <v>4</v>
       </c>
       <c r="I100" t="str">
-        <f>IF(A100&lt;&gt;B100,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
         <v>4</v>
       </c>
       <c r="I101" t="str">
-        <f>IF(A101&lt;&gt;B101,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
         <v>4</v>
       </c>
       <c r="I102" t="str">
-        <f>IF(A102&lt;&gt;B102,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
         <v>4</v>
       </c>
       <c r="I103" t="str">
-        <f>IF(A103&lt;&gt;B103,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
         <v>4</v>
       </c>
       <c r="I104" t="str">
-        <f>IF(A104&lt;&gt;B104,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
         <v>4</v>
       </c>
       <c r="I105" t="str">
-        <f>IF(A105&lt;&gt;B105,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
         <v>4</v>
       </c>
       <c r="I106" t="str">
-        <f>IF(A106&lt;&gt;B106,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v>FLAG</v>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
         <v>4</v>
       </c>
       <c r="I107" t="str">
-        <f>IF(A107&lt;&gt;B107,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
         <v>4</v>
       </c>
       <c r="I108" t="str">
-        <f>IF(A108&lt;&gt;B108,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
         <v>4</v>
       </c>
       <c r="I109" t="str">
-        <f>IF(A109&lt;&gt;B109,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
         <v>4</v>
       </c>
       <c r="I110" t="str">
-        <f>IF(A110&lt;&gt;B110,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
         <v>4</v>
       </c>
       <c r="I111" t="str">
-        <f>IF(A111&lt;&gt;B111,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
         <v>4</v>
       </c>
       <c r="I112" t="str">
-        <f>IF(A112&lt;&gt;B112,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
         <v>4</v>
       </c>
       <c r="I113" t="str">
-        <f>IF(A113&lt;&gt;B113,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
         <v>4</v>
       </c>
       <c r="I114" t="str">
-        <f>IF(A114&lt;&gt;B114,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         <v>4</v>
       </c>
       <c r="I115" t="str">
-        <f>IF(A115&lt;&gt;B115,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
         <v>4</v>
       </c>
       <c r="I116" t="str">
-        <f>IF(A116&lt;&gt;B116,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
         <v>4</v>
       </c>
       <c r="I117" t="str">
-        <f>IF(A117&lt;&gt;B117,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
         <v>4</v>
       </c>
       <c r="I118" t="str">
-        <f>IF(A118&lt;&gt;B118,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
         <v>4</v>
       </c>
       <c r="I119" t="str">
-        <f>IF(A119&lt;&gt;B119,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
         <v>4</v>
       </c>
       <c r="I120" t="str">
-        <f>IF(A120&lt;&gt;B120,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I114">
-    <cfRule type="containsText" dxfId="0" priority="31" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="2" priority="31" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
@@ -5950,7 +5950,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5965,7 +5965,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">

--- a/tabular/reference/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/reference/herv_sublineage_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4404761-373A-A34C-9F76-40382190E543}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE8340C-8FE1-F549-A3B2-C853C890DA1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="500" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="202">
   <si>
     <t>LTR_name</t>
   </si>
@@ -307,9 +307,6 @@
     <t>HUERS-P2</t>
   </si>
   <si>
-    <t>LTR1A1</t>
-  </si>
-  <si>
     <t>LTR1A2</t>
   </si>
   <si>
@@ -457,9 +454,6 @@
     <t>MLT2E</t>
   </si>
   <si>
-    <t>ERV-Le</t>
-  </si>
-  <si>
     <t>ERV3-16A3_LTR</t>
   </si>
   <si>
@@ -662,6 +656,9 @@
   </si>
   <si>
     <t>LTR-53</t>
+  </si>
+  <si>
+    <t>HERV-L74</t>
   </si>
 </sst>
 </file>
@@ -817,7 +814,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1015,12 +1012,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.24994659260841701"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1182,13 +1173,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1595,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1615,16 +1605,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -1633,7 +1623,7 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1644,7 +1634,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1653,7 +1643,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -1674,7 +1664,7 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1683,7 +1673,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
@@ -1704,7 +1694,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -1713,7 +1703,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -1734,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1743,7 +1733,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -1764,7 +1754,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1773,7 +1763,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G6" t="s">
         <v>9</v>
@@ -1794,7 +1784,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -1803,7 +1793,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
@@ -1824,7 +1814,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -1833,7 +1823,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G8" t="s">
         <v>9</v>
@@ -1854,7 +1844,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -1863,7 +1853,7 @@
         <v>23</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G9" t="s">
         <v>9</v>
@@ -1884,7 +1874,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -1893,7 +1883,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G10" t="s">
         <v>9</v>
@@ -1914,7 +1904,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
@@ -1923,7 +1913,7 @@
         <v>25</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G11" t="s">
         <v>9</v>
@@ -1944,7 +1934,7 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -1953,7 +1943,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G12" t="s">
         <v>9</v>
@@ -1974,7 +1964,7 @@
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
@@ -1983,7 +1973,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G13" t="s">
         <v>9</v>
@@ -2004,7 +1994,7 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
@@ -2013,7 +2003,7 @@
         <v>29</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G14" t="s">
         <v>9</v>
@@ -2034,7 +2024,7 @@
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
@@ -2043,7 +2033,7 @@
         <v>29</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G15" t="s">
         <v>9</v>
@@ -2064,7 +2054,7 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
         <v>29</v>
@@ -2073,7 +2063,7 @@
         <v>29</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G16" t="s">
         <v>9</v>
@@ -2094,7 +2084,7 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D17" t="s">
         <v>33</v>
@@ -2103,7 +2093,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G17" t="s">
         <v>9</v>
@@ -2124,7 +2114,7 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
@@ -2133,7 +2123,7 @@
         <v>36</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G18" t="s">
         <v>9</v>
@@ -2154,7 +2144,7 @@
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
         <v>38</v>
@@ -2163,7 +2153,7 @@
         <v>38</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G19" t="s">
         <v>9</v>
@@ -2184,7 +2174,7 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
@@ -2193,7 +2183,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G20" t="s">
         <v>9</v>
@@ -2214,7 +2204,7 @@
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D21" t="s">
         <v>38</v>
@@ -2223,7 +2213,7 @@
         <v>38</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G21" t="s">
         <v>9</v>
@@ -2244,7 +2234,7 @@
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D22" t="s">
         <v>38</v>
@@ -2253,7 +2243,7 @@
         <v>38</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G22" t="s">
         <v>9</v>
@@ -2274,7 +2264,7 @@
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
         <v>38</v>
@@ -2283,7 +2273,7 @@
         <v>38</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G23" t="s">
         <v>9</v>
@@ -2304,7 +2294,7 @@
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D24" t="s">
         <v>38</v>
@@ -2313,7 +2303,7 @@
         <v>38</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G24" t="s">
         <v>9</v>
@@ -2334,7 +2324,7 @@
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D25" t="s">
         <v>38</v>
@@ -2343,7 +2333,7 @@
         <v>38</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G25" t="s">
         <v>9</v>
@@ -2364,7 +2354,7 @@
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
@@ -2373,7 +2363,7 @@
         <v>38</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G26" t="s">
         <v>9</v>
@@ -2394,7 +2384,7 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
@@ -2403,7 +2393,7 @@
         <v>38</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G27" t="s">
         <v>9</v>
@@ -2424,7 +2414,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D28" t="s">
         <v>38</v>
@@ -2433,7 +2423,7 @@
         <v>38</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G28" t="s">
         <v>9</v>
@@ -2454,7 +2444,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D29" t="s">
         <v>49</v>
@@ -2463,7 +2453,7 @@
         <v>49</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G29" t="s">
         <v>9</v>
@@ -2484,7 +2474,7 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D30" t="s">
         <v>51</v>
@@ -2493,7 +2483,7 @@
         <v>51</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G30" t="s">
         <v>9</v>
@@ -2514,7 +2504,7 @@
         <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D31" t="s">
         <v>53</v>
@@ -2523,7 +2513,7 @@
         <v>53</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G31" t="s">
         <v>9</v>
@@ -2544,7 +2534,7 @@
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D32" t="s">
         <v>53</v>
@@ -2553,7 +2543,7 @@
         <v>53</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G32" t="s">
         <v>9</v>
@@ -2574,7 +2564,7 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D33" t="s">
         <v>53</v>
@@ -2583,7 +2573,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G33" t="s">
         <v>9</v>
@@ -2604,7 +2594,7 @@
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D34" t="s">
         <v>53</v>
@@ -2613,7 +2603,7 @@
         <v>53</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G34" t="s">
         <v>9</v>
@@ -2634,7 +2624,7 @@
         <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D35" t="s">
         <v>58</v>
@@ -2643,7 +2633,7 @@
         <v>58</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G35" t="s">
         <v>9</v>
@@ -2664,7 +2654,7 @@
         <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D36" t="s">
         <v>62</v>
@@ -2673,7 +2663,7 @@
         <v>62</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G36" t="s">
         <v>59</v>
@@ -2694,7 +2684,7 @@
         <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -2703,7 +2693,7 @@
         <v>62</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G37" t="s">
         <v>59</v>
@@ -2724,7 +2714,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
         <v>62</v>
@@ -2733,7 +2723,7 @@
         <v>62</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G38" t="s">
         <v>59</v>
@@ -2754,7 +2744,7 @@
         <v>63</v>
       </c>
       <c r="C39" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D39" t="s">
         <v>62</v>
@@ -2763,7 +2753,7 @@
         <v>62</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G39" t="s">
         <v>59</v>
@@ -2784,7 +2774,7 @@
         <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D40" t="s">
         <v>62</v>
@@ -2793,7 +2783,7 @@
         <v>62</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G40" t="s">
         <v>59</v>
@@ -2814,7 +2804,7 @@
         <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D41" t="s">
         <v>62</v>
@@ -2823,7 +2813,7 @@
         <v>62</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G41" t="s">
         <v>59</v>
@@ -2844,7 +2834,7 @@
         <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D42" t="s">
         <v>71</v>
@@ -2853,7 +2843,7 @@
         <v>71</v>
       </c>
       <c r="F42" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G42" t="s">
         <v>59</v>
@@ -2874,7 +2864,7 @@
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D43" t="s">
         <v>73</v>
@@ -2883,7 +2873,7 @@
         <v>73</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G43" t="s">
         <v>59</v>
@@ -2904,7 +2894,7 @@
         <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D44" t="s">
         <v>73</v>
@@ -2913,7 +2903,7 @@
         <v>73</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G44" t="s">
         <v>59</v>
@@ -2934,7 +2924,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D45" t="s">
         <v>76</v>
@@ -2943,7 +2933,7 @@
         <v>76</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G45" t="s">
         <v>59</v>
@@ -2964,7 +2954,7 @@
         <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
         <v>76</v>
@@ -2973,7 +2963,7 @@
         <v>76</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G46" t="s">
         <v>59</v>
@@ -2994,7 +2984,7 @@
         <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D47" t="s">
         <v>76</v>
@@ -3003,7 +2993,7 @@
         <v>76</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G47" t="s">
         <v>59</v>
@@ -3024,7 +3014,7 @@
         <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D48" t="s">
         <v>76</v>
@@ -3033,7 +3023,7 @@
         <v>76</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G48" t="s">
         <v>59</v>
@@ -3054,7 +3044,7 @@
         <v>80</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D49" t="s">
         <v>76</v>
@@ -3063,7 +3053,7 @@
         <v>76</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G49" t="s">
         <v>59</v>
@@ -3084,7 +3074,7 @@
         <v>81</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
         <v>76</v>
@@ -3093,7 +3083,7 @@
         <v>76</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G50" t="s">
         <v>59</v>
@@ -3114,7 +3104,7 @@
         <v>82</v>
       </c>
       <c r="C51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D51" t="s">
         <v>83</v>
@@ -3123,7 +3113,7 @@
         <v>83</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G51" t="s">
         <v>59</v>
@@ -3144,7 +3134,7 @@
         <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D52" t="s">
         <v>83</v>
@@ -3153,7 +3143,7 @@
         <v>83</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G52" t="s">
         <v>59</v>
@@ -3174,7 +3164,7 @@
         <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D53" t="s">
         <v>83</v>
@@ -3183,7 +3173,7 @@
         <v>83</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G53" t="s">
         <v>59</v>
@@ -3204,7 +3194,7 @@
         <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D54" t="s">
         <v>83</v>
@@ -3213,7 +3203,7 @@
         <v>83</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G54" t="s">
         <v>59</v>
@@ -3234,7 +3224,7 @@
         <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D55" t="s">
         <v>83</v>
@@ -3243,7 +3233,7 @@
         <v>83</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G55" t="s">
         <v>59</v>
@@ -3264,7 +3254,7 @@
         <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D56" t="s">
         <v>83</v>
@@ -3273,7 +3263,7 @@
         <v>83</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G56" t="s">
         <v>59</v>
@@ -3294,7 +3284,7 @@
         <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D57" t="s">
         <v>83</v>
@@ -3303,7 +3293,7 @@
         <v>83</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G57" t="s">
         <v>59</v>
@@ -3324,7 +3314,7 @@
         <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D58" t="s">
         <v>83</v>
@@ -3333,7 +3323,7 @@
         <v>83</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G58" t="s">
         <v>59</v>
@@ -3354,7 +3344,7 @@
         <v>91</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
         <v>83</v>
@@ -3363,7 +3353,7 @@
         <v>83</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G59" t="s">
         <v>59</v>
@@ -3384,7 +3374,7 @@
         <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D60" t="s">
         <v>83</v>
@@ -3393,7 +3383,7 @@
         <v>83</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G60" t="s">
         <v>59</v>
@@ -3414,7 +3404,7 @@
         <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D61" t="s">
         <v>83</v>
@@ -3423,7 +3413,7 @@
         <v>83</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G61" t="s">
         <v>59</v>
@@ -3444,7 +3434,7 @@
         <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D62" t="s">
         <v>83</v>
@@ -3453,7 +3443,7 @@
         <v>83</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G62" t="s">
         <v>59</v>
@@ -3474,7 +3464,7 @@
         <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D63" t="s">
         <v>83</v>
@@ -3483,7 +3473,7 @@
         <v>83</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G63" t="s">
         <v>59</v>
@@ -3504,7 +3494,7 @@
         <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D64" t="s">
         <v>83</v>
@@ -3513,7 +3503,7 @@
         <v>83</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G64" t="s">
         <v>59</v>
@@ -3534,7 +3524,7 @@
         <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D65" t="s">
         <v>83</v>
@@ -3543,7 +3533,7 @@
         <v>83</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G65" t="s">
         <v>59</v>
@@ -3564,7 +3554,7 @@
         <v>98</v>
       </c>
       <c r="C66" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D66" t="s">
         <v>83</v>
@@ -3573,7 +3563,7 @@
         <v>83</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G66" t="s">
         <v>59</v>
@@ -3594,16 +3584,16 @@
         <v>99</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D67" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E67" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G67" t="s">
         <v>59</v>
@@ -3617,23 +3607,23 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="5" t="s">
+      <c r="A68" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" t="s">
         <v>100</v>
       </c>
-      <c r="B68" t="s">
+      <c r="E68" t="s">
         <v>100</v>
       </c>
-      <c r="C68" t="s">
-        <v>191</v>
-      </c>
-      <c r="D68" t="s">
-        <v>101</v>
-      </c>
-      <c r="E68" t="s">
-        <v>101</v>
-      </c>
       <c r="F68" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G68" t="s">
         <v>59</v>
@@ -3647,23 +3637,23 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="5" t="s">
+      <c r="A69" t="s">
         <v>102</v>
       </c>
       <c r="B69" t="s">
         <v>102</v>
       </c>
       <c r="C69" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G69" t="s">
         <v>59</v>
@@ -3677,23 +3667,23 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
+      <c r="A70" t="s">
         <v>103</v>
       </c>
       <c r="B70" t="s">
         <v>103</v>
       </c>
       <c r="C70" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G70" t="s">
         <v>59</v>
@@ -3707,23 +3697,23 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="5" t="s">
+      <c r="A71" t="s">
         <v>104</v>
       </c>
       <c r="B71" t="s">
         <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G71" t="s">
         <v>59</v>
@@ -3737,23 +3727,23 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
+      <c r="A72" t="s">
         <v>105</v>
       </c>
       <c r="B72" t="s">
         <v>105</v>
       </c>
       <c r="C72" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D72" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E72" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G72" t="s">
         <v>59</v>
@@ -3768,22 +3758,22 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>107</v>
+      </c>
+      <c r="B73" t="s">
+        <v>107</v>
+      </c>
+      <c r="C73" t="s">
+        <v>189</v>
+      </c>
+      <c r="D73" t="s">
         <v>106</v>
       </c>
-      <c r="B73" t="s">
+      <c r="E73" t="s">
         <v>106</v>
       </c>
-      <c r="C73" t="s">
-        <v>191</v>
-      </c>
-      <c r="D73" t="s">
-        <v>107</v>
-      </c>
-      <c r="E73" t="s">
-        <v>107</v>
-      </c>
       <c r="F73" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G73" t="s">
         <v>59</v>
@@ -3804,16 +3794,16 @@
         <v>108</v>
       </c>
       <c r="C74" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G74" t="s">
         <v>59</v>
@@ -3834,16 +3824,16 @@
         <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G75" t="s">
         <v>59</v>
@@ -3864,16 +3854,16 @@
         <v>110</v>
       </c>
       <c r="C76" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G76" t="s">
         <v>59</v>
@@ -3894,16 +3884,16 @@
         <v>111</v>
       </c>
       <c r="C77" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G77" t="s">
         <v>59</v>
@@ -3924,16 +3914,16 @@
         <v>112</v>
       </c>
       <c r="C78" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G78" t="s">
         <v>59</v>
@@ -3954,16 +3944,16 @@
         <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G79" t="s">
         <v>59</v>
@@ -3984,16 +3974,16 @@
         <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G80" t="s">
         <v>59</v>
@@ -4014,16 +4004,16 @@
         <v>115</v>
       </c>
       <c r="C81" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G81" t="s">
         <v>59</v>
@@ -4044,16 +4034,16 @@
         <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G82" t="s">
         <v>59</v>
@@ -4074,16 +4064,16 @@
         <v>117</v>
       </c>
       <c r="C83" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G83" t="s">
         <v>59</v>
@@ -4104,16 +4094,16 @@
         <v>118</v>
       </c>
       <c r="C84" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D84" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E84" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G84" t="s">
         <v>59</v>
@@ -4128,22 +4118,22 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B85" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E85" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G85" t="s">
         <v>59</v>
@@ -4158,22 +4148,22 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>122</v>
+      </c>
+      <c r="B86" t="s">
+        <v>122</v>
+      </c>
+      <c r="C86" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" t="s">
         <v>121</v>
       </c>
-      <c r="B86" t="s">
+      <c r="E86" t="s">
         <v>121</v>
       </c>
-      <c r="C86" t="s">
-        <v>191</v>
-      </c>
-      <c r="D86" t="s">
-        <v>122</v>
-      </c>
-      <c r="E86" t="s">
-        <v>122</v>
-      </c>
       <c r="F86" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G86" t="s">
         <v>59</v>
@@ -4194,16 +4184,16 @@
         <v>123</v>
       </c>
       <c r="C87" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D87" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E87" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G87" t="s">
         <v>59</v>
@@ -4218,25 +4208,25 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B88" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E88" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G88" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="H88" t="s">
         <v>4</v>
@@ -4248,25 +4238,25 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>130</v>
+      </c>
+      <c r="B89" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" t="s">
+        <v>190</v>
+      </c>
+      <c r="D89" t="s">
+        <v>131</v>
+      </c>
+      <c r="E89" t="s">
+        <v>131</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G89" t="s">
         <v>128</v>
-      </c>
-      <c r="B89" t="s">
-        <v>128</v>
-      </c>
-      <c r="C89" t="s">
-        <v>192</v>
-      </c>
-      <c r="D89" t="s">
-        <v>130</v>
-      </c>
-      <c r="E89" t="s">
-        <v>130</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G89" t="s">
-        <v>129</v>
       </c>
       <c r="H89" t="s">
         <v>4</v>
@@ -4278,25 +4268,25 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C90" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D90" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E90" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G90" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -4314,7 +4304,7 @@
         <v>133</v>
       </c>
       <c r="C91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D91" t="s">
         <v>134</v>
@@ -4323,10 +4313,10 @@
         <v>134</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H91" t="s">
         <v>4</v>
@@ -4344,19 +4334,19 @@
         <v>135</v>
       </c>
       <c r="C92" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D92" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E92" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -4368,25 +4358,25 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C93" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D93" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E93" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H93" t="s">
         <v>4</v>
@@ -4398,25 +4388,25 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B94" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C94" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D94" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E94" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H94" t="s">
         <v>4</v>
@@ -4428,25 +4418,25 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B95" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C95" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E95" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H95" t="s">
         <v>4</v>
@@ -4458,25 +4448,25 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D96" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E96" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H96" t="s">
         <v>4</v>
@@ -4488,25 +4478,25 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C97" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E97" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H97" t="s">
         <v>4</v>
@@ -4518,55 +4508,55 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C98" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D98" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E98" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H98" t="s">
         <v>4</v>
       </c>
       <c r="I98" t="str">
-        <f t="shared" ref="I98:I120" si="3">IF(A98&lt;&gt;B98,"FLAG","")</f>
+        <f t="shared" ref="I98:I117" si="3">IF(A98&lt;&gt;B98,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B99" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C99" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E99" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H99" t="s">
         <v>4</v>
@@ -4578,25 +4568,25 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C100" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E100" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H100" t="s">
         <v>4</v>
@@ -4608,25 +4598,25 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B101" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C101" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E101" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G101" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H101" t="s">
         <v>4</v>
@@ -4638,25 +4628,25 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B102" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C102" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D102" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E102" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H102" t="s">
         <v>4</v>
@@ -4668,25 +4658,25 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C103" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D103" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E103" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H103" t="s">
         <v>4</v>
@@ -4698,25 +4688,25 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>147</v>
+      </c>
+      <c r="B104" t="s">
+        <v>147</v>
+      </c>
+      <c r="C104" t="s">
+        <v>190</v>
+      </c>
+      <c r="D104" t="s">
         <v>148</v>
       </c>
-      <c r="B104" t="s">
+      <c r="E104" t="s">
         <v>148</v>
       </c>
-      <c r="C104" t="s">
-        <v>192</v>
-      </c>
-      <c r="D104" t="s">
-        <v>136</v>
-      </c>
-      <c r="E104" t="s">
-        <v>136</v>
-      </c>
       <c r="F104" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G104" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H104" t="s">
         <v>4</v>
@@ -4728,85 +4718,85 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B105" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C105" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D105" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="E105" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G105" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H105" t="s">
         <v>4</v>
       </c>
       <c r="I105" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C106" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D106" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E106" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G106" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H106" t="s">
         <v>4</v>
       </c>
       <c r="I106" t="str">
         <f t="shared" si="3"/>
-        <v>FLAG</v>
+        <v/>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B107" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C107" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D107" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E107" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G107" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H107" t="s">
         <v>4</v>
@@ -4818,25 +4808,25 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B108" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C108" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D108" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E108" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G108" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H108" t="s">
         <v>4</v>
@@ -4854,19 +4844,19 @@
         <v>159</v>
       </c>
       <c r="C109" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D109" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E109" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G109" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H109" t="s">
         <v>4</v>
@@ -4881,22 +4871,22 @@
         <v>160</v>
       </c>
       <c r="B110" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C110" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D110" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E110" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G110" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H110" t="s">
         <v>4</v>
@@ -4908,25 +4898,25 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B111" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C111" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D111" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E111" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H111" t="s">
         <v>4</v>
@@ -4938,25 +4928,25 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B112" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C112" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D112" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E112" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H112" t="s">
         <v>4</v>
@@ -4968,25 +4958,25 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>163</v>
+      </c>
+      <c r="B113" t="s">
+        <v>163</v>
+      </c>
+      <c r="C113" t="s">
+        <v>190</v>
+      </c>
+      <c r="D113" t="s">
+        <v>201</v>
+      </c>
+      <c r="E113" t="s">
         <v>164</v>
       </c>
-      <c r="B113" t="s">
-        <v>164</v>
-      </c>
-      <c r="C113" t="s">
-        <v>192</v>
-      </c>
-      <c r="D113" t="s">
-        <v>200</v>
-      </c>
-      <c r="E113" t="s">
-        <v>200</v>
-      </c>
       <c r="F113" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H113" t="s">
         <v>4</v>
@@ -4998,25 +4988,25 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B114" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C114" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D114" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E114" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G114" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H114" t="s">
         <v>4</v>
@@ -5028,25 +5018,25 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B115" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C115" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D115" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="E115" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G115" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H115" t="s">
         <v>4</v>
@@ -5058,25 +5048,25 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>170</v>
+      </c>
+      <c r="B116" t="s">
+        <v>170</v>
+      </c>
+      <c r="C116" t="s">
+        <v>190</v>
+      </c>
+      <c r="D116" t="s">
         <v>168</v>
       </c>
-      <c r="B116" t="s">
+      <c r="E116" t="s">
         <v>168</v>
       </c>
-      <c r="C116" t="s">
-        <v>192</v>
-      </c>
-      <c r="D116" t="s">
-        <v>202</v>
-      </c>
-      <c r="E116" t="s">
-        <v>202</v>
-      </c>
       <c r="F116" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G116" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H116" t="s">
         <v>4</v>
@@ -5088,25 +5078,25 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B117" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C117" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D117" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E117" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G117" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H117" t="s">
         <v>4</v>
@@ -5116,106 +5106,16 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>171</v>
-      </c>
-      <c r="B118" t="s">
-        <v>171</v>
-      </c>
-      <c r="C118" t="s">
-        <v>192</v>
-      </c>
-      <c r="D118" t="s">
-        <v>170</v>
-      </c>
-      <c r="E118" t="s">
-        <v>170</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G118" t="s">
-        <v>129</v>
-      </c>
-      <c r="H118" t="s">
-        <v>4</v>
-      </c>
-      <c r="I118" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>172</v>
-      </c>
-      <c r="B119" t="s">
-        <v>172</v>
-      </c>
-      <c r="C119" t="s">
-        <v>192</v>
-      </c>
-      <c r="D119" t="s">
-        <v>170</v>
-      </c>
-      <c r="E119" t="s">
-        <v>170</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G119" t="s">
-        <v>129</v>
-      </c>
-      <c r="H119" t="s">
-        <v>4</v>
-      </c>
-      <c r="I119" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>173</v>
-      </c>
-      <c r="B120" t="s">
-        <v>173</v>
-      </c>
-      <c r="C120" t="s">
-        <v>192</v>
-      </c>
-      <c r="D120" t="s">
-        <v>174</v>
-      </c>
-      <c r="E120" t="s">
-        <v>174</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G120" t="s">
-        <v>129</v>
-      </c>
-      <c r="H120" t="s">
-        <v>4</v>
-      </c>
-      <c r="I120" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
-    <sortCondition ref="C2:C120"/>
-    <sortCondition ref="G2:G120"/>
-    <sortCondition ref="H2:H120"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I117">
+    <sortCondition ref="C2:C117"/>
+    <sortCondition ref="G2:G117"/>
+    <sortCondition ref="H2:H117"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="I117:I118">
+  <conditionalFormatting sqref="I114:I115">
     <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I117)))</formula>
+      <formula>NOT(ISERROR(SEARCH("FLAG",I114)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -5228,26 +5128,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I115:I116">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I115)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I114">
-    <cfRule type="containsText" dxfId="2" priority="31" operator="containsText" text="FLAG">
+  <conditionalFormatting sqref="I2:I113">
+    <cfRule type="containsText" dxfId="3" priority="33" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5264,7 +5149,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC7E8D0-101B-584C-9021-A7CDF92F27AF}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -5275,16 +5160,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -5293,18 +5178,18 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -5328,13 +5213,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -5358,13 +5243,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -5388,13 +5273,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -5418,13 +5303,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -5448,13 +5333,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -5478,13 +5363,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -5508,13 +5393,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
@@ -5538,13 +5423,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -5568,13 +5453,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -5598,13 +5483,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -5628,13 +5513,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
@@ -5658,13 +5543,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -5688,13 +5573,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
@@ -5718,13 +5603,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -5744,13 +5629,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
@@ -5776,7 +5661,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
@@ -5800,13 +5685,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
@@ -5836,7 +5721,7 @@
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
@@ -5866,7 +5751,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
@@ -5896,16 +5781,16 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -5920,25 +5805,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
         <v>4</v>
@@ -5948,10 +5833,85 @@
         <v>FLAG</v>
       </c>
     </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" t="str">
+        <f>IF(A24&lt;&gt;B24,"FLAG","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E25" t="s">
+        <v>200</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G25" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" t="str">
+        <f>IF(A25&lt;&gt;B25,"FLAG","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -5964,9 +5924,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I23">
+  <conditionalFormatting sqref="I24:I25">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
+      <formula>NOT(ISERROR(SEARCH("FLAG",I24)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>

--- a/tabular/reference/herv_sublineage_ltr_data_all.xlsx
+++ b/tabular/reference/herv_sublineage_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE8340C-8FE1-F549-A3B2-C853C890DA1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3B3A5E-D031-914D-8370-53276289CE4B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="500" windowWidth="27480" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
